--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/1750000/Output_8_12.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/1750000/Output_8_12.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>89243.13053484244</v>
+        <v>99118.00245785525</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7085693.356097211</v>
+        <v>5923717.618902254</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22436727.51434465</v>
+        <v>22594091.76629887</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4126904.064616508</v>
+        <v>4128123.760379126</v>
       </c>
     </row>
     <row r="11">
@@ -8667,28 +8667,28 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>144.5373969889978</v>
+        <v>169.0966151720738</v>
       </c>
       <c r="K11" t="n">
-        <v>165.3730621002569</v>
+        <v>202.1809638361346</v>
       </c>
       <c r="L11" t="n">
-        <v>167.8853998946103</v>
+        <v>213.5488567752802</v>
       </c>
       <c r="M11" t="n">
-        <v>154.8155246845592</v>
+        <v>205.6249188705004</v>
       </c>
       <c r="N11" t="n">
-        <v>152.6601892247316</v>
+        <v>204.2917325281876</v>
       </c>
       <c r="O11" t="n">
-        <v>157.6226486076164</v>
+        <v>206.3768508508745</v>
       </c>
       <c r="P11" t="n">
-        <v>169.3767796748675</v>
+        <v>210.9873633211545</v>
       </c>
       <c r="Q11" t="n">
-        <v>175.8542476633942</v>
+        <v>207.1020630664799</v>
       </c>
       <c r="R11" t="n">
         <v>65.71641987298243</v>
@@ -8746,28 +8746,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J12" t="n">
-        <v>105.0934096855346</v>
+        <v>119.7207117878867</v>
       </c>
       <c r="K12" t="n">
-        <v>100.6771087856797</v>
+        <v>125.6774978810001</v>
       </c>
       <c r="L12" t="n">
-        <v>88.58235147798737</v>
+        <v>122.1984598562864</v>
       </c>
       <c r="M12" t="n">
-        <v>83.81903392201832</v>
+        <v>123.047446830095</v>
       </c>
       <c r="N12" t="n">
-        <v>71.48328755503141</v>
+        <v>111.7499598249992</v>
       </c>
       <c r="O12" t="n">
-        <v>87.83748029350105</v>
+        <v>124.673618687554</v>
       </c>
       <c r="P12" t="n">
-        <v>90.02567156527363</v>
+        <v>119.5899201578276</v>
       </c>
       <c r="Q12" t="n">
-        <v>110.6032080482857</v>
+        <v>130.3661252938572</v>
       </c>
       <c r="R12" t="n">
         <v>45.52166981132082</v>
@@ -8828,22 +8828,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K13" t="n">
-        <v>106.5958811213551</v>
+        <v>106.7437663446525</v>
       </c>
       <c r="L13" t="n">
-        <v>106.1981516910743</v>
+        <v>125.4955336943436</v>
       </c>
       <c r="M13" t="n">
-        <v>108.6798659148182</v>
+        <v>129.0262495446563</v>
       </c>
       <c r="N13" t="n">
-        <v>98.15880676031514</v>
+        <v>118.0213988638392</v>
       </c>
       <c r="O13" t="n">
-        <v>111.1838171403674</v>
+        <v>129.5301358016631</v>
       </c>
       <c r="P13" t="n">
-        <v>114.3914794589837</v>
+        <v>130.0899244982092</v>
       </c>
       <c r="Q13" t="n">
         <v>65.34295837775146</v>
@@ -8904,28 +8904,28 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>144.5373969889978</v>
+        <v>169.0966151720738</v>
       </c>
       <c r="K14" t="n">
-        <v>165.3730621002569</v>
+        <v>202.1809638361346</v>
       </c>
       <c r="L14" t="n">
-        <v>167.8853998946103</v>
+        <v>213.5488567752802</v>
       </c>
       <c r="M14" t="n">
-        <v>154.8155246845592</v>
+        <v>205.6249188705004</v>
       </c>
       <c r="N14" t="n">
-        <v>152.6601892247316</v>
+        <v>204.2917325281876</v>
       </c>
       <c r="O14" t="n">
-        <v>157.6226486076164</v>
+        <v>206.3768508508745</v>
       </c>
       <c r="P14" t="n">
-        <v>169.3767796748675</v>
+        <v>210.9873633211545</v>
       </c>
       <c r="Q14" t="n">
-        <v>175.8542476633942</v>
+        <v>207.1020630664799</v>
       </c>
       <c r="R14" t="n">
         <v>65.71641987298243</v>
@@ -8983,28 +8983,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J15" t="n">
-        <v>105.0934096855346</v>
+        <v>119.7207117878867</v>
       </c>
       <c r="K15" t="n">
-        <v>100.6771087856797</v>
+        <v>125.6774978810001</v>
       </c>
       <c r="L15" t="n">
-        <v>88.58235147798737</v>
+        <v>122.1984598562864</v>
       </c>
       <c r="M15" t="n">
-        <v>83.81903392201832</v>
+        <v>123.047446830095</v>
       </c>
       <c r="N15" t="n">
-        <v>71.48328755503141</v>
+        <v>111.7499598249992</v>
       </c>
       <c r="O15" t="n">
-        <v>87.83748029350105</v>
+        <v>124.673618687554</v>
       </c>
       <c r="P15" t="n">
-        <v>90.02567156527363</v>
+        <v>119.5899201578276</v>
       </c>
       <c r="Q15" t="n">
-        <v>110.6032080482857</v>
+        <v>130.3661252938572</v>
       </c>
       <c r="R15" t="n">
         <v>45.52166981132082</v>
@@ -9065,22 +9065,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K16" t="n">
-        <v>106.5958811213551</v>
+        <v>106.7437663446525</v>
       </c>
       <c r="L16" t="n">
-        <v>106.1981516910743</v>
+        <v>125.4955336943436</v>
       </c>
       <c r="M16" t="n">
-        <v>108.6798659148182</v>
+        <v>129.0262495446563</v>
       </c>
       <c r="N16" t="n">
-        <v>98.15880676031514</v>
+        <v>118.0213988638392</v>
       </c>
       <c r="O16" t="n">
-        <v>111.1838171403674</v>
+        <v>129.5301358016631</v>
       </c>
       <c r="P16" t="n">
-        <v>114.3914794589837</v>
+        <v>130.0899244982092</v>
       </c>
       <c r="Q16" t="n">
         <v>65.34295837775146</v>
@@ -9141,28 +9141,28 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>144.5373969889978</v>
+        <v>169.0966151720738</v>
       </c>
       <c r="K17" t="n">
-        <v>165.3730621002569</v>
+        <v>202.1809638361346</v>
       </c>
       <c r="L17" t="n">
-        <v>167.8853998946103</v>
+        <v>213.5488567752802</v>
       </c>
       <c r="M17" t="n">
-        <v>154.8155246845592</v>
+        <v>205.6249188705004</v>
       </c>
       <c r="N17" t="n">
-        <v>152.6601892247316</v>
+        <v>204.2917325281876</v>
       </c>
       <c r="O17" t="n">
-        <v>157.6226486076164</v>
+        <v>206.3768508508745</v>
       </c>
       <c r="P17" t="n">
-        <v>169.3767796748675</v>
+        <v>210.9873633211545</v>
       </c>
       <c r="Q17" t="n">
-        <v>175.8542476633942</v>
+        <v>207.1020630664799</v>
       </c>
       <c r="R17" t="n">
         <v>65.71641987298243</v>
@@ -9220,28 +9220,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J18" t="n">
-        <v>105.0934096855346</v>
+        <v>119.7207117878867</v>
       </c>
       <c r="K18" t="n">
-        <v>100.6771087856797</v>
+        <v>125.6774978810001</v>
       </c>
       <c r="L18" t="n">
-        <v>88.58235147798737</v>
+        <v>122.1984598562864</v>
       </c>
       <c r="M18" t="n">
-        <v>83.81903392201832</v>
+        <v>123.047446830095</v>
       </c>
       <c r="N18" t="n">
-        <v>71.48328755503141</v>
+        <v>111.7499598249992</v>
       </c>
       <c r="O18" t="n">
-        <v>87.83748029350105</v>
+        <v>124.673618687554</v>
       </c>
       <c r="P18" t="n">
-        <v>90.02567156527363</v>
+        <v>119.5899201578276</v>
       </c>
       <c r="Q18" t="n">
-        <v>110.6032080482857</v>
+        <v>130.3661252938572</v>
       </c>
       <c r="R18" t="n">
         <v>45.52166981132082</v>
@@ -9302,22 +9302,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K19" t="n">
-        <v>106.5958811213551</v>
+        <v>106.7437663446525</v>
       </c>
       <c r="L19" t="n">
-        <v>106.1981516910743</v>
+        <v>125.4955336943436</v>
       </c>
       <c r="M19" t="n">
-        <v>108.6798659148182</v>
+        <v>129.0262495446563</v>
       </c>
       <c r="N19" t="n">
-        <v>98.15880676031514</v>
+        <v>118.0213988638392</v>
       </c>
       <c r="O19" t="n">
-        <v>111.1838171403674</v>
+        <v>129.5301358016631</v>
       </c>
       <c r="P19" t="n">
-        <v>114.3914794589837</v>
+        <v>130.0899244982092</v>
       </c>
       <c r="Q19" t="n">
         <v>65.34295837775146</v>
@@ -9378,28 +9378,28 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>144.5373969889978</v>
+        <v>169.0966151720738</v>
       </c>
       <c r="K20" t="n">
-        <v>165.3730621002569</v>
+        <v>202.1809638361346</v>
       </c>
       <c r="L20" t="n">
-        <v>167.8853998946103</v>
+        <v>213.5488567752802</v>
       </c>
       <c r="M20" t="n">
-        <v>154.8155246845592</v>
+        <v>205.6249188705004</v>
       </c>
       <c r="N20" t="n">
-        <v>152.6601892247316</v>
+        <v>204.2917325281876</v>
       </c>
       <c r="O20" t="n">
-        <v>157.6226486076164</v>
+        <v>206.3768508508745</v>
       </c>
       <c r="P20" t="n">
-        <v>169.3767796748675</v>
+        <v>210.9873633211545</v>
       </c>
       <c r="Q20" t="n">
-        <v>175.8542476633942</v>
+        <v>207.1020630664799</v>
       </c>
       <c r="R20" t="n">
         <v>65.71641987298243</v>
@@ -9457,28 +9457,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J21" t="n">
-        <v>105.0934096855346</v>
+        <v>119.7207117878867</v>
       </c>
       <c r="K21" t="n">
-        <v>100.6771087856797</v>
+        <v>125.6774978810001</v>
       </c>
       <c r="L21" t="n">
-        <v>88.58235147798737</v>
+        <v>122.1984598562864</v>
       </c>
       <c r="M21" t="n">
-        <v>83.81903392201832</v>
+        <v>123.047446830095</v>
       </c>
       <c r="N21" t="n">
-        <v>71.48328755503141</v>
+        <v>111.7499598249992</v>
       </c>
       <c r="O21" t="n">
-        <v>87.83748029350105</v>
+        <v>124.673618687554</v>
       </c>
       <c r="P21" t="n">
-        <v>90.02567156527363</v>
+        <v>119.5899201578276</v>
       </c>
       <c r="Q21" t="n">
-        <v>110.6032080482857</v>
+        <v>130.3661252938572</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9539,22 +9539,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K22" t="n">
-        <v>106.5958811213551</v>
+        <v>106.7437663446525</v>
       </c>
       <c r="L22" t="n">
-        <v>106.1981516910743</v>
+        <v>125.4955336943436</v>
       </c>
       <c r="M22" t="n">
-        <v>108.6798659148182</v>
+        <v>129.0262495446563</v>
       </c>
       <c r="N22" t="n">
-        <v>98.15880676031514</v>
+        <v>118.0213988638392</v>
       </c>
       <c r="O22" t="n">
-        <v>111.1838171403674</v>
+        <v>129.5301358016631</v>
       </c>
       <c r="P22" t="n">
-        <v>114.3914794589837</v>
+        <v>130.0899244982092</v>
       </c>
       <c r="Q22" t="n">
         <v>65.34295837775146</v>
@@ -9615,28 +9615,28 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>144.5373969889978</v>
+        <v>169.0966151720738</v>
       </c>
       <c r="K23" t="n">
-        <v>165.3730621002569</v>
+        <v>202.1809638361346</v>
       </c>
       <c r="L23" t="n">
-        <v>167.8853998946103</v>
+        <v>213.5488567752802</v>
       </c>
       <c r="M23" t="n">
-        <v>154.8155246845592</v>
+        <v>205.6249188705004</v>
       </c>
       <c r="N23" t="n">
-        <v>152.6601892247316</v>
+        <v>204.2917325281876</v>
       </c>
       <c r="O23" t="n">
-        <v>157.6226486076164</v>
+        <v>206.3768508508745</v>
       </c>
       <c r="P23" t="n">
-        <v>169.3767796748675</v>
+        <v>210.9873633211545</v>
       </c>
       <c r="Q23" t="n">
-        <v>175.8542476633942</v>
+        <v>207.1020630664799</v>
       </c>
       <c r="R23" t="n">
         <v>65.71641987298243</v>
@@ -9694,28 +9694,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J24" t="n">
-        <v>105.0934096855346</v>
+        <v>119.7207117878867</v>
       </c>
       <c r="K24" t="n">
-        <v>100.6771087856797</v>
+        <v>125.6774978810001</v>
       </c>
       <c r="L24" t="n">
-        <v>88.58235147798737</v>
+        <v>122.1984598562864</v>
       </c>
       <c r="M24" t="n">
-        <v>83.81903392201832</v>
+        <v>123.047446830095</v>
       </c>
       <c r="N24" t="n">
-        <v>71.48328755503141</v>
+        <v>111.7499598249992</v>
       </c>
       <c r="O24" t="n">
-        <v>87.83748029350105</v>
+        <v>124.673618687554</v>
       </c>
       <c r="P24" t="n">
-        <v>90.02567156527363</v>
+        <v>119.5899201578276</v>
       </c>
       <c r="Q24" t="n">
-        <v>110.6032080482857</v>
+        <v>130.3661252938572</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9776,22 +9776,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K25" t="n">
-        <v>106.5958811213551</v>
+        <v>106.7437663446525</v>
       </c>
       <c r="L25" t="n">
-        <v>106.1981516910743</v>
+        <v>125.4955336943436</v>
       </c>
       <c r="M25" t="n">
-        <v>108.6798659148182</v>
+        <v>129.0262495446563</v>
       </c>
       <c r="N25" t="n">
-        <v>98.15880676031514</v>
+        <v>118.0213988638392</v>
       </c>
       <c r="O25" t="n">
-        <v>111.1838171403674</v>
+        <v>129.5301358016631</v>
       </c>
       <c r="P25" t="n">
-        <v>114.3914794589837</v>
+        <v>130.0899244982092</v>
       </c>
       <c r="Q25" t="n">
         <v>65.34295837775146</v>
@@ -9852,28 +9852,28 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>144.5373969889978</v>
+        <v>169.0966151720738</v>
       </c>
       <c r="K26" t="n">
-        <v>165.3730621002569</v>
+        <v>202.1809638361346</v>
       </c>
       <c r="L26" t="n">
-        <v>167.8853998946103</v>
+        <v>213.5488567752802</v>
       </c>
       <c r="M26" t="n">
-        <v>154.8155246845592</v>
+        <v>205.6249188705004</v>
       </c>
       <c r="N26" t="n">
-        <v>152.6601892247316</v>
+        <v>204.2917325281876</v>
       </c>
       <c r="O26" t="n">
-        <v>157.6226486076164</v>
+        <v>206.3768508508745</v>
       </c>
       <c r="P26" t="n">
-        <v>169.3767796748675</v>
+        <v>210.9873633211545</v>
       </c>
       <c r="Q26" t="n">
-        <v>175.8542476633942</v>
+        <v>207.1020630664798</v>
       </c>
       <c r="R26" t="n">
         <v>65.71641987298243</v>
@@ -9931,28 +9931,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J27" t="n">
-        <v>105.0934096855346</v>
+        <v>119.7207117878867</v>
       </c>
       <c r="K27" t="n">
-        <v>100.6771087856797</v>
+        <v>125.6774978810001</v>
       </c>
       <c r="L27" t="n">
-        <v>88.58235147798737</v>
+        <v>122.1984598562864</v>
       </c>
       <c r="M27" t="n">
-        <v>83.81903392201832</v>
+        <v>123.047446830095</v>
       </c>
       <c r="N27" t="n">
-        <v>71.48328755503141</v>
+        <v>111.7499598249992</v>
       </c>
       <c r="O27" t="n">
-        <v>87.83748029350105</v>
+        <v>124.673618687554</v>
       </c>
       <c r="P27" t="n">
-        <v>90.02567156527363</v>
+        <v>119.5899201578276</v>
       </c>
       <c r="Q27" t="n">
-        <v>110.6032080482857</v>
+        <v>130.3661252938572</v>
       </c>
       <c r="R27" t="n">
         <v>45.52166981132082</v>
@@ -10013,22 +10013,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K28" t="n">
-        <v>106.5958811213551</v>
+        <v>106.7437663446525</v>
       </c>
       <c r="L28" t="n">
-        <v>106.1981516910743</v>
+        <v>125.4955336943436</v>
       </c>
       <c r="M28" t="n">
-        <v>108.6798659148182</v>
+        <v>129.0262495446562</v>
       </c>
       <c r="N28" t="n">
-        <v>98.15880676031514</v>
+        <v>118.0213988638391</v>
       </c>
       <c r="O28" t="n">
-        <v>111.1838171403674</v>
+        <v>129.5301358016631</v>
       </c>
       <c r="P28" t="n">
-        <v>114.3914794589837</v>
+        <v>130.0899244982092</v>
       </c>
       <c r="Q28" t="n">
         <v>65.34295837775146</v>
@@ -10089,28 +10089,28 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>144.5373969889978</v>
+        <v>169.0966151720738</v>
       </c>
       <c r="K29" t="n">
-        <v>165.3730621002569</v>
+        <v>202.1809638361346</v>
       </c>
       <c r="L29" t="n">
-        <v>167.8853998946103</v>
+        <v>213.5488567752802</v>
       </c>
       <c r="M29" t="n">
-        <v>154.8155246845592</v>
+        <v>205.6249188705004</v>
       </c>
       <c r="N29" t="n">
-        <v>152.6601892247316</v>
+        <v>204.2917325281876</v>
       </c>
       <c r="O29" t="n">
-        <v>157.6226486076164</v>
+        <v>206.3768508508745</v>
       </c>
       <c r="P29" t="n">
-        <v>169.3767796748675</v>
+        <v>210.9873633211545</v>
       </c>
       <c r="Q29" t="n">
-        <v>175.8542476633942</v>
+        <v>207.1020630664799</v>
       </c>
       <c r="R29" t="n">
         <v>65.71641987298243</v>
@@ -10168,28 +10168,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J30" t="n">
-        <v>105.0934096855346</v>
+        <v>119.7207117878867</v>
       </c>
       <c r="K30" t="n">
-        <v>100.6771087856797</v>
+        <v>125.6774978810001</v>
       </c>
       <c r="L30" t="n">
-        <v>88.58235147798737</v>
+        <v>122.1984598562864</v>
       </c>
       <c r="M30" t="n">
-        <v>83.81903392201832</v>
+        <v>123.047446830095</v>
       </c>
       <c r="N30" t="n">
-        <v>71.48328755503141</v>
+        <v>111.7499598249992</v>
       </c>
       <c r="O30" t="n">
-        <v>87.83748029350105</v>
+        <v>124.673618687554</v>
       </c>
       <c r="P30" t="n">
-        <v>90.02567156527363</v>
+        <v>119.5899201578276</v>
       </c>
       <c r="Q30" t="n">
-        <v>110.6032080482857</v>
+        <v>130.3661252938572</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10250,22 +10250,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K31" t="n">
-        <v>106.5958811213551</v>
+        <v>106.7437663446525</v>
       </c>
       <c r="L31" t="n">
-        <v>106.1981516910743</v>
+        <v>125.4955336943436</v>
       </c>
       <c r="M31" t="n">
-        <v>108.6798659148182</v>
+        <v>129.0262495446563</v>
       </c>
       <c r="N31" t="n">
-        <v>98.15880676031514</v>
+        <v>118.0213988638392</v>
       </c>
       <c r="O31" t="n">
-        <v>111.1838171403674</v>
+        <v>129.5301358016631</v>
       </c>
       <c r="P31" t="n">
-        <v>114.3914794589837</v>
+        <v>130.0899244982092</v>
       </c>
       <c r="Q31" t="n">
         <v>65.34295837775146</v>
@@ -10326,28 +10326,28 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>144.5373969889978</v>
+        <v>169.0966151720738</v>
       </c>
       <c r="K32" t="n">
-        <v>165.3730621002569</v>
+        <v>202.1809638361346</v>
       </c>
       <c r="L32" t="n">
-        <v>167.8853998946103</v>
+        <v>213.5488567752802</v>
       </c>
       <c r="M32" t="n">
-        <v>154.8155246845592</v>
+        <v>205.6249188705004</v>
       </c>
       <c r="N32" t="n">
-        <v>152.6601892247316</v>
+        <v>204.2917325281876</v>
       </c>
       <c r="O32" t="n">
-        <v>157.6226486076164</v>
+        <v>206.3768508508745</v>
       </c>
       <c r="P32" t="n">
-        <v>169.3767796748675</v>
+        <v>210.9873633211545</v>
       </c>
       <c r="Q32" t="n">
-        <v>175.8542476633942</v>
+        <v>207.1020630664799</v>
       </c>
       <c r="R32" t="n">
         <v>65.71641987298243</v>
@@ -10405,28 +10405,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J33" t="n">
-        <v>105.0934096855346</v>
+        <v>119.7207117878867</v>
       </c>
       <c r="K33" t="n">
-        <v>100.6771087856797</v>
+        <v>125.6774978810001</v>
       </c>
       <c r="L33" t="n">
-        <v>88.58235147798737</v>
+        <v>122.1984598562864</v>
       </c>
       <c r="M33" t="n">
-        <v>83.81903392201832</v>
+        <v>123.047446830095</v>
       </c>
       <c r="N33" t="n">
-        <v>71.48328755503141</v>
+        <v>111.7499598249992</v>
       </c>
       <c r="O33" t="n">
-        <v>87.83748029350105</v>
+        <v>124.673618687554</v>
       </c>
       <c r="P33" t="n">
-        <v>90.02567156527363</v>
+        <v>119.5899201578276</v>
       </c>
       <c r="Q33" t="n">
-        <v>110.6032080482857</v>
+        <v>130.3661252938572</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10487,22 +10487,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K34" t="n">
-        <v>106.5958811213551</v>
+        <v>106.7437663446525</v>
       </c>
       <c r="L34" t="n">
-        <v>106.1981516910743</v>
+        <v>125.4955336943436</v>
       </c>
       <c r="M34" t="n">
-        <v>108.6798659148182</v>
+        <v>129.0262495446563</v>
       </c>
       <c r="N34" t="n">
-        <v>98.15880676031514</v>
+        <v>118.0213988638392</v>
       </c>
       <c r="O34" t="n">
-        <v>111.1838171403674</v>
+        <v>129.5301358016631</v>
       </c>
       <c r="P34" t="n">
-        <v>114.3914794589837</v>
+        <v>130.0899244982092</v>
       </c>
       <c r="Q34" t="n">
         <v>65.34295837775146</v>
@@ -10563,28 +10563,28 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>144.5373969889978</v>
+        <v>169.0966151720738</v>
       </c>
       <c r="K35" t="n">
-        <v>165.3730621002569</v>
+        <v>202.1809638361346</v>
       </c>
       <c r="L35" t="n">
-        <v>167.8853998946103</v>
+        <v>213.5488567752802</v>
       </c>
       <c r="M35" t="n">
-        <v>154.8155246845592</v>
+        <v>205.6249188705004</v>
       </c>
       <c r="N35" t="n">
-        <v>152.6601892247316</v>
+        <v>204.2917325281876</v>
       </c>
       <c r="O35" t="n">
-        <v>157.6226486076164</v>
+        <v>206.3768508508745</v>
       </c>
       <c r="P35" t="n">
-        <v>169.3767796748675</v>
+        <v>210.9873633211545</v>
       </c>
       <c r="Q35" t="n">
-        <v>175.8542476633942</v>
+        <v>207.1020630664799</v>
       </c>
       <c r="R35" t="n">
         <v>65.71641987298243</v>
@@ -10642,28 +10642,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J36" t="n">
-        <v>105.0934096855346</v>
+        <v>119.7207117878867</v>
       </c>
       <c r="K36" t="n">
-        <v>100.6771087856797</v>
+        <v>125.6774978810001</v>
       </c>
       <c r="L36" t="n">
-        <v>88.58235147798737</v>
+        <v>122.1984598562864</v>
       </c>
       <c r="M36" t="n">
-        <v>83.81903392201832</v>
+        <v>123.047446830095</v>
       </c>
       <c r="N36" t="n">
-        <v>71.48328755503141</v>
+        <v>111.7499598249992</v>
       </c>
       <c r="O36" t="n">
-        <v>87.83748029350105</v>
+        <v>124.673618687554</v>
       </c>
       <c r="P36" t="n">
-        <v>90.02567156527363</v>
+        <v>119.5899201578276</v>
       </c>
       <c r="Q36" t="n">
-        <v>110.6032080482857</v>
+        <v>130.3661252938572</v>
       </c>
       <c r="R36" t="n">
         <v>45.52166981132082</v>
@@ -10724,22 +10724,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K37" t="n">
-        <v>106.5958811213551</v>
+        <v>106.7437663446525</v>
       </c>
       <c r="L37" t="n">
-        <v>106.1981516910743</v>
+        <v>125.4955336943436</v>
       </c>
       <c r="M37" t="n">
-        <v>108.6798659148182</v>
+        <v>129.0262495446563</v>
       </c>
       <c r="N37" t="n">
-        <v>98.15880676031514</v>
+        <v>118.0213988638392</v>
       </c>
       <c r="O37" t="n">
-        <v>111.1838171403674</v>
+        <v>129.5301358016631</v>
       </c>
       <c r="P37" t="n">
-        <v>114.3914794589837</v>
+        <v>130.0899244982092</v>
       </c>
       <c r="Q37" t="n">
         <v>65.34295837775146</v>
@@ -10800,28 +10800,28 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>144.5373969889978</v>
+        <v>169.0966151720738</v>
       </c>
       <c r="K38" t="n">
-        <v>165.3730621002569</v>
+        <v>202.1809638361346</v>
       </c>
       <c r="L38" t="n">
-        <v>167.8853998946103</v>
+        <v>213.5488567752802</v>
       </c>
       <c r="M38" t="n">
-        <v>154.8155246845592</v>
+        <v>205.6249188705004</v>
       </c>
       <c r="N38" t="n">
-        <v>152.6601892247316</v>
+        <v>204.2917325281876</v>
       </c>
       <c r="O38" t="n">
-        <v>157.6226486076164</v>
+        <v>206.3768508508745</v>
       </c>
       <c r="P38" t="n">
-        <v>169.3767796748675</v>
+        <v>210.9873633211545</v>
       </c>
       <c r="Q38" t="n">
-        <v>175.8542476633942</v>
+        <v>207.1020630664799</v>
       </c>
       <c r="R38" t="n">
         <v>65.71641987298243</v>
@@ -10879,28 +10879,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J39" t="n">
-        <v>105.0934096855346</v>
+        <v>119.7207117878867</v>
       </c>
       <c r="K39" t="n">
-        <v>100.6771087856797</v>
+        <v>125.6774978810001</v>
       </c>
       <c r="L39" t="n">
-        <v>88.58235147798737</v>
+        <v>122.1984598562864</v>
       </c>
       <c r="M39" t="n">
-        <v>83.81903392201832</v>
+        <v>123.047446830095</v>
       </c>
       <c r="N39" t="n">
-        <v>71.48328755503141</v>
+        <v>111.7499598249992</v>
       </c>
       <c r="O39" t="n">
-        <v>87.83748029350105</v>
+        <v>124.673618687554</v>
       </c>
       <c r="P39" t="n">
-        <v>90.02567156527363</v>
+        <v>119.5899201578276</v>
       </c>
       <c r="Q39" t="n">
-        <v>110.6032080482857</v>
+        <v>130.3661252938572</v>
       </c>
       <c r="R39" t="n">
         <v>45.52166981132082</v>
@@ -10961,22 +10961,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K40" t="n">
-        <v>106.5958811213551</v>
+        <v>106.7437663446525</v>
       </c>
       <c r="L40" t="n">
-        <v>106.1981516910743</v>
+        <v>125.4955336943436</v>
       </c>
       <c r="M40" t="n">
-        <v>108.6798659148182</v>
+        <v>129.0262495446563</v>
       </c>
       <c r="N40" t="n">
-        <v>98.15880676031514</v>
+        <v>118.0213988638392</v>
       </c>
       <c r="O40" t="n">
-        <v>111.1838171403674</v>
+        <v>129.5301358016631</v>
       </c>
       <c r="P40" t="n">
-        <v>114.3914794589837</v>
+        <v>130.0899244982092</v>
       </c>
       <c r="Q40" t="n">
         <v>65.34295837775146</v>
@@ -11037,28 +11037,28 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>144.5373969889978</v>
+        <v>169.0966151720738</v>
       </c>
       <c r="K41" t="n">
-        <v>165.3730621002569</v>
+        <v>202.1809638361346</v>
       </c>
       <c r="L41" t="n">
-        <v>167.8853998946103</v>
+        <v>213.5488567752802</v>
       </c>
       <c r="M41" t="n">
-        <v>154.8155246845592</v>
+        <v>205.6249188705004</v>
       </c>
       <c r="N41" t="n">
-        <v>152.6601892247316</v>
+        <v>204.2917325281876</v>
       </c>
       <c r="O41" t="n">
-        <v>157.6226486076164</v>
+        <v>206.3768508508745</v>
       </c>
       <c r="P41" t="n">
-        <v>169.3767796748675</v>
+        <v>210.9873633211545</v>
       </c>
       <c r="Q41" t="n">
-        <v>175.8542476633942</v>
+        <v>207.1020630664799</v>
       </c>
       <c r="R41" t="n">
         <v>65.71641987298243</v>
@@ -11116,28 +11116,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J42" t="n">
-        <v>105.0934096855346</v>
+        <v>119.7207117878867</v>
       </c>
       <c r="K42" t="n">
-        <v>100.6771087856797</v>
+        <v>125.6774978810001</v>
       </c>
       <c r="L42" t="n">
-        <v>88.58235147798737</v>
+        <v>122.1984598562864</v>
       </c>
       <c r="M42" t="n">
-        <v>83.81903392201832</v>
+        <v>123.047446830095</v>
       </c>
       <c r="N42" t="n">
-        <v>71.48328755503141</v>
+        <v>111.7499598249992</v>
       </c>
       <c r="O42" t="n">
-        <v>87.83748029350105</v>
+        <v>124.673618687554</v>
       </c>
       <c r="P42" t="n">
-        <v>90.02567156527363</v>
+        <v>119.5899201578276</v>
       </c>
       <c r="Q42" t="n">
-        <v>110.6032080482857</v>
+        <v>130.3661252938572</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -11198,22 +11198,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K43" t="n">
-        <v>106.5958811213551</v>
+        <v>106.7437663446525</v>
       </c>
       <c r="L43" t="n">
-        <v>106.1981516910743</v>
+        <v>125.4955336943436</v>
       </c>
       <c r="M43" t="n">
-        <v>108.6798659148182</v>
+        <v>129.0262495446563</v>
       </c>
       <c r="N43" t="n">
-        <v>98.15880676031514</v>
+        <v>118.0213988638392</v>
       </c>
       <c r="O43" t="n">
-        <v>111.1838171403674</v>
+        <v>129.5301358016631</v>
       </c>
       <c r="P43" t="n">
-        <v>114.3914794589837</v>
+        <v>130.0899244982092</v>
       </c>
       <c r="Q43" t="n">
         <v>65.34295837775146</v>
@@ -11274,28 +11274,28 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>144.5373969889978</v>
+        <v>169.0966151720738</v>
       </c>
       <c r="K44" t="n">
-        <v>165.3730621002569</v>
+        <v>202.1809638361346</v>
       </c>
       <c r="L44" t="n">
-        <v>167.8853998946103</v>
+        <v>213.5488567752802</v>
       </c>
       <c r="M44" t="n">
-        <v>154.8155246845592</v>
+        <v>205.6249188705004</v>
       </c>
       <c r="N44" t="n">
-        <v>152.6601892247316</v>
+        <v>204.2917325281876</v>
       </c>
       <c r="O44" t="n">
-        <v>157.6226486076164</v>
+        <v>206.3768508508745</v>
       </c>
       <c r="P44" t="n">
-        <v>169.3767796748675</v>
+        <v>210.9873633211545</v>
       </c>
       <c r="Q44" t="n">
-        <v>175.8542476633942</v>
+        <v>207.1020630664799</v>
       </c>
       <c r="R44" t="n">
         <v>65.71641987298243</v>
@@ -11353,28 +11353,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J45" t="n">
-        <v>105.0934096855346</v>
+        <v>119.7207117878867</v>
       </c>
       <c r="K45" t="n">
-        <v>100.6771087856797</v>
+        <v>125.6774978810001</v>
       </c>
       <c r="L45" t="n">
-        <v>88.58235147798737</v>
+        <v>122.1984598562864</v>
       </c>
       <c r="M45" t="n">
-        <v>83.81903392201832</v>
+        <v>123.047446830095</v>
       </c>
       <c r="N45" t="n">
-        <v>71.48328755503141</v>
+        <v>111.7499598249992</v>
       </c>
       <c r="O45" t="n">
-        <v>87.83748029350105</v>
+        <v>124.673618687554</v>
       </c>
       <c r="P45" t="n">
-        <v>90.02567156527363</v>
+        <v>119.5899201578276</v>
       </c>
       <c r="Q45" t="n">
-        <v>110.6032080482857</v>
+        <v>130.3661252938572</v>
       </c>
       <c r="R45" t="n">
         <v>45.52166981132082</v>
@@ -11435,22 +11435,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K46" t="n">
-        <v>106.5958811213551</v>
+        <v>106.7437663446525</v>
       </c>
       <c r="L46" t="n">
-        <v>106.1981516910743</v>
+        <v>125.4955336943436</v>
       </c>
       <c r="M46" t="n">
-        <v>108.6798659148182</v>
+        <v>129.0262495446563</v>
       </c>
       <c r="N46" t="n">
-        <v>98.15880676031514</v>
+        <v>118.0213988638392</v>
       </c>
       <c r="O46" t="n">
-        <v>111.1838171403674</v>
+        <v>129.5301358016631</v>
       </c>
       <c r="P46" t="n">
-        <v>114.3914794589837</v>
+        <v>130.0899244982092</v>
       </c>
       <c r="Q46" t="n">
         <v>65.34295837775146</v>
@@ -23230,13 +23230,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G11" t="n">
-        <v>414.8725867613662</v>
+        <v>415.1619485273195</v>
       </c>
       <c r="H11" t="n">
-        <v>335.069520708732</v>
+        <v>338.0329468943008</v>
       </c>
       <c r="I11" t="n">
-        <v>193.8925026357325</v>
+        <v>205.0481221176458</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -23263,16 +23263,16 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>122.8486606547175</v>
+        <v>141.0252816852793</v>
       </c>
       <c r="S11" t="n">
-        <v>199.2180092847378</v>
+        <v>205.8118405263978</v>
       </c>
       <c r="T11" t="n">
-        <v>221.2128646395082</v>
+        <v>222.4795457699687</v>
       </c>
       <c r="U11" t="n">
-        <v>251.311240847535</v>
+        <v>251.3343897888113</v>
       </c>
       <c r="V11" t="n">
         <v>327.7522584701349</v>
@@ -23309,13 +23309,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G12" t="n">
-        <v>137.1133662198144</v>
+        <v>137.2681884137393</v>
       </c>
       <c r="H12" t="n">
-        <v>110.0126706515908</v>
+        <v>111.5079271034444</v>
       </c>
       <c r="I12" t="n">
-        <v>81.47257624764148</v>
+        <v>86.80307722268741</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -23342,16 +23342,16 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>85.8682869828318</v>
+        <v>95.48084390037957</v>
       </c>
       <c r="S12" t="n">
-        <v>167.4082182736491</v>
+        <v>170.2839726213331</v>
       </c>
       <c r="T12" t="n">
-        <v>199.2370588835009</v>
+        <v>199.8611009721718</v>
       </c>
       <c r="U12" t="n">
-        <v>225.9262405715409</v>
+        <v>225.9364262421938</v>
       </c>
       <c r="V12" t="n">
         <v>232.8005871494253</v>
@@ -23388,19 +23388,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G13" t="n">
-        <v>167.7980285387866</v>
+        <v>167.9278262653587</v>
       </c>
       <c r="H13" t="n">
-        <v>160.5116643107183</v>
+        <v>161.6656840978772</v>
       </c>
       <c r="I13" t="n">
-        <v>149.6479175502091</v>
+        <v>153.551289182031</v>
       </c>
       <c r="J13" t="n">
-        <v>79.71755716585311</v>
+        <v>88.89425643449839</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>14.93225064571201</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -23418,19 +23418,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>70.00504325169439</v>
+        <v>80.87383288310646</v>
       </c>
       <c r="R13" t="n">
-        <v>168.6176208853662</v>
+        <v>174.4537986637794</v>
       </c>
       <c r="S13" t="n">
-        <v>220.6539914795952</v>
+        <v>222.9160118599466</v>
       </c>
       <c r="T13" t="n">
-        <v>227.1211631987733</v>
+        <v>227.6757534850358</v>
       </c>
       <c r="U13" t="n">
-        <v>286.308504766327</v>
+        <v>286.3155846423218</v>
       </c>
       <c r="V13" t="n">
         <v>252.137643323828</v>
@@ -23467,13 +23467,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G14" t="n">
-        <v>414.8725867613662</v>
+        <v>415.1619485273195</v>
       </c>
       <c r="H14" t="n">
-        <v>335.069520708732</v>
+        <v>338.0329468943008</v>
       </c>
       <c r="I14" t="n">
-        <v>193.8925026357325</v>
+        <v>205.0481221176458</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -23500,16 +23500,16 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>122.8486606547175</v>
+        <v>141.0252816852793</v>
       </c>
       <c r="S14" t="n">
-        <v>199.2180092847378</v>
+        <v>205.8118405263978</v>
       </c>
       <c r="T14" t="n">
-        <v>221.2128646395082</v>
+        <v>222.4795457699687</v>
       </c>
       <c r="U14" t="n">
-        <v>251.311240847535</v>
+        <v>251.3343897888113</v>
       </c>
       <c r="V14" t="n">
         <v>327.7522584701349</v>
@@ -23546,13 +23546,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G15" t="n">
-        <v>137.1133662198144</v>
+        <v>137.2681884137393</v>
       </c>
       <c r="H15" t="n">
-        <v>110.0126706515908</v>
+        <v>111.5079271034444</v>
       </c>
       <c r="I15" t="n">
-        <v>81.47257624764148</v>
+        <v>86.80307722268741</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -23579,16 +23579,16 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>85.8682869828318</v>
+        <v>95.48084390037957</v>
       </c>
       <c r="S15" t="n">
-        <v>167.4082182736491</v>
+        <v>170.2839726213331</v>
       </c>
       <c r="T15" t="n">
-        <v>199.2370588835009</v>
+        <v>199.8611009721718</v>
       </c>
       <c r="U15" t="n">
-        <v>225.9262405715409</v>
+        <v>225.9364262421938</v>
       </c>
       <c r="V15" t="n">
         <v>232.8005871494253</v>
@@ -23625,19 +23625,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G16" t="n">
-        <v>167.7980285387866</v>
+        <v>167.9278262653587</v>
       </c>
       <c r="H16" t="n">
-        <v>160.5116643107183</v>
+        <v>161.6656840978772</v>
       </c>
       <c r="I16" t="n">
-        <v>149.6479175502091</v>
+        <v>153.551289182031</v>
       </c>
       <c r="J16" t="n">
-        <v>79.71755716585311</v>
+        <v>88.89425643449839</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>14.93225064571201</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -23655,19 +23655,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>70.00504325169439</v>
+        <v>80.87383288310646</v>
       </c>
       <c r="R16" t="n">
-        <v>168.6176208853662</v>
+        <v>174.4537986637794</v>
       </c>
       <c r="S16" t="n">
-        <v>220.6539914795952</v>
+        <v>222.9160118599466</v>
       </c>
       <c r="T16" t="n">
-        <v>227.1211631987733</v>
+        <v>227.6757534850358</v>
       </c>
       <c r="U16" t="n">
-        <v>286.308504766327</v>
+        <v>286.3155846423218</v>
       </c>
       <c r="V16" t="n">
         <v>252.137643323828</v>
@@ -23704,13 +23704,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G17" t="n">
-        <v>414.8725867613662</v>
+        <v>415.1619485273195</v>
       </c>
       <c r="H17" t="n">
-        <v>335.069520708732</v>
+        <v>338.0329468943008</v>
       </c>
       <c r="I17" t="n">
-        <v>193.8925026357325</v>
+        <v>205.0481221176458</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -23737,16 +23737,16 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>122.8486606547175</v>
+        <v>141.0252816852793</v>
       </c>
       <c r="S17" t="n">
-        <v>199.2180092847378</v>
+        <v>205.8118405263978</v>
       </c>
       <c r="T17" t="n">
-        <v>221.2128646395082</v>
+        <v>222.4795457699687</v>
       </c>
       <c r="U17" t="n">
-        <v>251.311240847535</v>
+        <v>251.3343897888113</v>
       </c>
       <c r="V17" t="n">
         <v>327.7522584701349</v>
@@ -23783,13 +23783,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G18" t="n">
-        <v>137.1133662198144</v>
+        <v>137.2681884137393</v>
       </c>
       <c r="H18" t="n">
-        <v>110.0126706515908</v>
+        <v>111.5079271034444</v>
       </c>
       <c r="I18" t="n">
-        <v>81.47257624764148</v>
+        <v>86.80307722268741</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -23816,16 +23816,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>85.8682869828318</v>
+        <v>95.48084390037957</v>
       </c>
       <c r="S18" t="n">
-        <v>167.4082182736491</v>
+        <v>170.2839726213331</v>
       </c>
       <c r="T18" t="n">
-        <v>199.2370588835009</v>
+        <v>199.8611009721718</v>
       </c>
       <c r="U18" t="n">
-        <v>225.9262405715409</v>
+        <v>225.9364262421938</v>
       </c>
       <c r="V18" t="n">
         <v>232.8005871494253</v>
@@ -23862,19 +23862,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G19" t="n">
-        <v>167.7980285387866</v>
+        <v>167.9278262653587</v>
       </c>
       <c r="H19" t="n">
-        <v>160.5116643107183</v>
+        <v>161.6656840978772</v>
       </c>
       <c r="I19" t="n">
-        <v>149.6479175502091</v>
+        <v>153.551289182031</v>
       </c>
       <c r="J19" t="n">
-        <v>79.71755716585311</v>
+        <v>88.89425643449839</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>14.93225064571201</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -23892,19 +23892,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>70.00504325169439</v>
+        <v>80.87383288310646</v>
       </c>
       <c r="R19" t="n">
-        <v>168.6176208853662</v>
+        <v>174.4537986637794</v>
       </c>
       <c r="S19" t="n">
-        <v>220.6539914795952</v>
+        <v>222.9160118599466</v>
       </c>
       <c r="T19" t="n">
-        <v>227.1211631987733</v>
+        <v>227.6757534850358</v>
       </c>
       <c r="U19" t="n">
-        <v>286.308504766327</v>
+        <v>286.3155846423218</v>
       </c>
       <c r="V19" t="n">
         <v>252.137643323828</v>
@@ -23941,13 +23941,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G20" t="n">
-        <v>414.8725867613662</v>
+        <v>415.1619485273195</v>
       </c>
       <c r="H20" t="n">
-        <v>335.069520708732</v>
+        <v>338.0329468943008</v>
       </c>
       <c r="I20" t="n">
-        <v>193.8925026357325</v>
+        <v>205.0481221176458</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -23974,16 +23974,16 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>122.8486606547175</v>
+        <v>141.0252816852793</v>
       </c>
       <c r="S20" t="n">
-        <v>199.2180092847378</v>
+        <v>205.8118405263978</v>
       </c>
       <c r="T20" t="n">
-        <v>221.2128646395082</v>
+        <v>222.4795457699687</v>
       </c>
       <c r="U20" t="n">
-        <v>251.311240847535</v>
+        <v>251.3343897888113</v>
       </c>
       <c r="V20" t="n">
         <v>327.7522584701349</v>
@@ -24020,13 +24020,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G21" t="n">
-        <v>137.1133662198144</v>
+        <v>137.2681884137393</v>
       </c>
       <c r="H21" t="n">
-        <v>110.0126706515908</v>
+        <v>111.5079271034444</v>
       </c>
       <c r="I21" t="n">
-        <v>81.47257624764148</v>
+        <v>86.80307722268741</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -24053,16 +24053,16 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>85.8682869828318</v>
+        <v>95.48084390037957</v>
       </c>
       <c r="S21" t="n">
-        <v>167.4082182736491</v>
+        <v>170.2839726213331</v>
       </c>
       <c r="T21" t="n">
-        <v>199.2370588835009</v>
+        <v>199.8611009721718</v>
       </c>
       <c r="U21" t="n">
-        <v>225.9262405715409</v>
+        <v>225.9364262421938</v>
       </c>
       <c r="V21" t="n">
         <v>232.8005871494253</v>
@@ -24099,19 +24099,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G22" t="n">
-        <v>167.7980285387866</v>
+        <v>167.9278262653587</v>
       </c>
       <c r="H22" t="n">
-        <v>160.5116643107183</v>
+        <v>161.6656840978772</v>
       </c>
       <c r="I22" t="n">
-        <v>149.6479175502091</v>
+        <v>153.551289182031</v>
       </c>
       <c r="J22" t="n">
-        <v>79.71755716585311</v>
+        <v>88.89425643449839</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>14.93225064571201</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -24129,19 +24129,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>70.00504325169439</v>
+        <v>80.87383288310646</v>
       </c>
       <c r="R22" t="n">
-        <v>168.6176208853662</v>
+        <v>174.4537986637794</v>
       </c>
       <c r="S22" t="n">
-        <v>220.6539914795952</v>
+        <v>222.9160118599466</v>
       </c>
       <c r="T22" t="n">
-        <v>227.1211631987733</v>
+        <v>227.6757534850358</v>
       </c>
       <c r="U22" t="n">
-        <v>286.308504766327</v>
+        <v>286.3155846423218</v>
       </c>
       <c r="V22" t="n">
         <v>252.137643323828</v>
@@ -24178,13 +24178,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G23" t="n">
-        <v>414.8725867613662</v>
+        <v>415.1619485273195</v>
       </c>
       <c r="H23" t="n">
-        <v>335.069520708732</v>
+        <v>338.0329468943008</v>
       </c>
       <c r="I23" t="n">
-        <v>193.8925026357325</v>
+        <v>205.0481221176458</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -24211,16 +24211,16 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>122.8486606547175</v>
+        <v>141.0252816852793</v>
       </c>
       <c r="S23" t="n">
-        <v>199.2180092847378</v>
+        <v>205.8118405263978</v>
       </c>
       <c r="T23" t="n">
-        <v>221.2128646395082</v>
+        <v>222.4795457699687</v>
       </c>
       <c r="U23" t="n">
-        <v>251.311240847535</v>
+        <v>251.3343897888113</v>
       </c>
       <c r="V23" t="n">
         <v>327.7522584701349</v>
@@ -24257,13 +24257,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
-        <v>137.1133662198144</v>
+        <v>137.2681884137393</v>
       </c>
       <c r="H24" t="n">
-        <v>110.0126706515908</v>
+        <v>111.5079271034444</v>
       </c>
       <c r="I24" t="n">
-        <v>81.47257624764148</v>
+        <v>86.80307722268741</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -24290,16 +24290,16 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>85.8682869828318</v>
+        <v>95.48084390037957</v>
       </c>
       <c r="S24" t="n">
-        <v>167.4082182736491</v>
+        <v>170.2839726213331</v>
       </c>
       <c r="T24" t="n">
-        <v>199.2370588835009</v>
+        <v>199.8611009721718</v>
       </c>
       <c r="U24" t="n">
-        <v>225.9262405715409</v>
+        <v>225.9364262421938</v>
       </c>
       <c r="V24" t="n">
         <v>232.8005871494253</v>
@@ -24336,19 +24336,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G25" t="n">
-        <v>167.7980285387866</v>
+        <v>167.9278262653587</v>
       </c>
       <c r="H25" t="n">
-        <v>160.5116643107183</v>
+        <v>161.6656840978772</v>
       </c>
       <c r="I25" t="n">
-        <v>149.6479175502091</v>
+        <v>153.551289182031</v>
       </c>
       <c r="J25" t="n">
-        <v>79.71755716585311</v>
+        <v>88.89425643449839</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>14.93225064571201</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -24366,19 +24366,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>70.00504325169439</v>
+        <v>80.87383288310646</v>
       </c>
       <c r="R25" t="n">
-        <v>168.6176208853662</v>
+        <v>174.4537986637794</v>
       </c>
       <c r="S25" t="n">
-        <v>220.6539914795952</v>
+        <v>222.9160118599466</v>
       </c>
       <c r="T25" t="n">
-        <v>227.1211631987733</v>
+        <v>227.6757534850358</v>
       </c>
       <c r="U25" t="n">
-        <v>286.308504766327</v>
+        <v>286.3155846423218</v>
       </c>
       <c r="V25" t="n">
         <v>252.137643323828</v>
@@ -24415,13 +24415,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G26" t="n">
-        <v>414.8725867613662</v>
+        <v>415.1619485273195</v>
       </c>
       <c r="H26" t="n">
-        <v>335.069520708732</v>
+        <v>338.0329468943008</v>
       </c>
       <c r="I26" t="n">
-        <v>193.8925026357325</v>
+        <v>205.0481221176458</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -24448,16 +24448,16 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>122.8486606547175</v>
+        <v>141.0252816852793</v>
       </c>
       <c r="S26" t="n">
-        <v>199.2180092847378</v>
+        <v>205.8118405263978</v>
       </c>
       <c r="T26" t="n">
-        <v>221.2128646395082</v>
+        <v>222.4795457699687</v>
       </c>
       <c r="U26" t="n">
-        <v>251.311240847535</v>
+        <v>251.3343897888113</v>
       </c>
       <c r="V26" t="n">
         <v>327.7522584701349</v>
@@ -24494,13 +24494,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G27" t="n">
-        <v>137.1133662198144</v>
+        <v>137.2681884137393</v>
       </c>
       <c r="H27" t="n">
-        <v>110.0126706515908</v>
+        <v>111.5079271034444</v>
       </c>
       <c r="I27" t="n">
-        <v>81.47257624764148</v>
+        <v>86.80307722268741</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -24527,16 +24527,16 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>85.8682869828318</v>
+        <v>95.48084390037957</v>
       </c>
       <c r="S27" t="n">
-        <v>167.4082182736491</v>
+        <v>170.2839726213331</v>
       </c>
       <c r="T27" t="n">
-        <v>199.2370588835009</v>
+        <v>199.8611009721718</v>
       </c>
       <c r="U27" t="n">
-        <v>225.9262405715409</v>
+        <v>225.9364262421938</v>
       </c>
       <c r="V27" t="n">
         <v>232.8005871494253</v>
@@ -24573,19 +24573,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G28" t="n">
-        <v>167.7980285387866</v>
+        <v>167.9278262653587</v>
       </c>
       <c r="H28" t="n">
-        <v>160.5116643107183</v>
+        <v>161.6656840978772</v>
       </c>
       <c r="I28" t="n">
-        <v>149.6479175502091</v>
+        <v>153.551289182031</v>
       </c>
       <c r="J28" t="n">
-        <v>79.71755716585311</v>
+        <v>88.89425643449839</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>14.93225064571201</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -24603,19 +24603,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>70.00504325169439</v>
+        <v>80.87383288310646</v>
       </c>
       <c r="R28" t="n">
-        <v>168.6176208853662</v>
+        <v>174.4537986637794</v>
       </c>
       <c r="S28" t="n">
-        <v>220.6539914795952</v>
+        <v>222.9160118599466</v>
       </c>
       <c r="T28" t="n">
-        <v>227.1211631987733</v>
+        <v>227.6757534850358</v>
       </c>
       <c r="U28" t="n">
-        <v>286.308504766327</v>
+        <v>286.3155846423218</v>
       </c>
       <c r="V28" t="n">
         <v>252.137643323828</v>
@@ -24652,13 +24652,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G29" t="n">
-        <v>414.8725867613662</v>
+        <v>415.1619485273195</v>
       </c>
       <c r="H29" t="n">
-        <v>335.069520708732</v>
+        <v>338.0329468943008</v>
       </c>
       <c r="I29" t="n">
-        <v>193.8925026357325</v>
+        <v>205.0481221176458</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -24685,16 +24685,16 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>122.8486606547175</v>
+        <v>141.0252816852793</v>
       </c>
       <c r="S29" t="n">
-        <v>199.2180092847378</v>
+        <v>205.8118405263978</v>
       </c>
       <c r="T29" t="n">
-        <v>221.2128646395082</v>
+        <v>222.4795457699687</v>
       </c>
       <c r="U29" t="n">
-        <v>251.311240847535</v>
+        <v>251.3343897888113</v>
       </c>
       <c r="V29" t="n">
         <v>327.7522584701349</v>
@@ -24731,13 +24731,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
-        <v>137.1133662198144</v>
+        <v>137.2681884137393</v>
       </c>
       <c r="H30" t="n">
-        <v>110.0126706515908</v>
+        <v>111.5079271034444</v>
       </c>
       <c r="I30" t="n">
-        <v>81.47257624764148</v>
+        <v>86.80307722268741</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -24764,16 +24764,16 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>85.8682869828318</v>
+        <v>95.48084390037957</v>
       </c>
       <c r="S30" t="n">
-        <v>167.4082182736491</v>
+        <v>170.2839726213331</v>
       </c>
       <c r="T30" t="n">
-        <v>199.2370588835009</v>
+        <v>199.8611009721718</v>
       </c>
       <c r="U30" t="n">
-        <v>225.9262405715409</v>
+        <v>225.9364262421938</v>
       </c>
       <c r="V30" t="n">
         <v>232.8005871494253</v>
@@ -24810,19 +24810,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G31" t="n">
-        <v>167.7980285387866</v>
+        <v>167.9278262653587</v>
       </c>
       <c r="H31" t="n">
-        <v>160.5116643107183</v>
+        <v>161.6656840978772</v>
       </c>
       <c r="I31" t="n">
-        <v>149.6479175502091</v>
+        <v>153.551289182031</v>
       </c>
       <c r="J31" t="n">
-        <v>79.71755716585311</v>
+        <v>88.89425643449839</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>14.93225064571201</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -24840,19 +24840,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>70.00504325169439</v>
+        <v>80.87383288310646</v>
       </c>
       <c r="R31" t="n">
-        <v>168.6176208853662</v>
+        <v>174.4537986637794</v>
       </c>
       <c r="S31" t="n">
-        <v>220.6539914795952</v>
+        <v>222.9160118599466</v>
       </c>
       <c r="T31" t="n">
-        <v>227.1211631987733</v>
+        <v>227.6757534850358</v>
       </c>
       <c r="U31" t="n">
-        <v>286.308504766327</v>
+        <v>286.3155846423218</v>
       </c>
       <c r="V31" t="n">
         <v>252.137643323828</v>
@@ -24889,13 +24889,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G32" t="n">
-        <v>414.8725867613662</v>
+        <v>415.1619485273195</v>
       </c>
       <c r="H32" t="n">
-        <v>335.069520708732</v>
+        <v>338.0329468943008</v>
       </c>
       <c r="I32" t="n">
-        <v>193.8925026357325</v>
+        <v>205.0481221176458</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -24922,16 +24922,16 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>122.8486606547175</v>
+        <v>141.0252816852793</v>
       </c>
       <c r="S32" t="n">
-        <v>199.2180092847378</v>
+        <v>205.8118405263978</v>
       </c>
       <c r="T32" t="n">
-        <v>221.2128646395082</v>
+        <v>222.4795457699687</v>
       </c>
       <c r="U32" t="n">
-        <v>251.311240847535</v>
+        <v>251.3343897888113</v>
       </c>
       <c r="V32" t="n">
         <v>327.7522584701349</v>
@@ -24968,13 +24968,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>137.1133662198144</v>
+        <v>137.2681884137393</v>
       </c>
       <c r="H33" t="n">
-        <v>110.0126706515908</v>
+        <v>111.5079271034444</v>
       </c>
       <c r="I33" t="n">
-        <v>81.47257624764148</v>
+        <v>86.80307722268741</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -25001,16 +25001,16 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>85.8682869828318</v>
+        <v>95.48084390037957</v>
       </c>
       <c r="S33" t="n">
-        <v>167.4082182736491</v>
+        <v>170.2839726213331</v>
       </c>
       <c r="T33" t="n">
-        <v>199.2370588835009</v>
+        <v>199.8611009721718</v>
       </c>
       <c r="U33" t="n">
-        <v>225.9262405715409</v>
+        <v>225.9364262421938</v>
       </c>
       <c r="V33" t="n">
         <v>232.8005871494253</v>
@@ -25047,19 +25047,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G34" t="n">
-        <v>167.7980285387866</v>
+        <v>167.9278262653587</v>
       </c>
       <c r="H34" t="n">
-        <v>160.5116643107183</v>
+        <v>161.6656840978772</v>
       </c>
       <c r="I34" t="n">
-        <v>149.6479175502091</v>
+        <v>153.551289182031</v>
       </c>
       <c r="J34" t="n">
-        <v>79.71755716585311</v>
+        <v>88.89425643449839</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>14.93225064571201</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -25077,19 +25077,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>70.00504325169439</v>
+        <v>80.87383288310646</v>
       </c>
       <c r="R34" t="n">
-        <v>168.6176208853662</v>
+        <v>174.4537986637794</v>
       </c>
       <c r="S34" t="n">
-        <v>220.6539914795952</v>
+        <v>222.9160118599466</v>
       </c>
       <c r="T34" t="n">
-        <v>227.1211631987733</v>
+        <v>227.6757534850358</v>
       </c>
       <c r="U34" t="n">
-        <v>286.308504766327</v>
+        <v>286.3155846423218</v>
       </c>
       <c r="V34" t="n">
         <v>252.137643323828</v>
@@ -25126,13 +25126,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G35" t="n">
-        <v>414.8725867613662</v>
+        <v>415.1619485273195</v>
       </c>
       <c r="H35" t="n">
-        <v>335.069520708732</v>
+        <v>338.0329468943008</v>
       </c>
       <c r="I35" t="n">
-        <v>193.8925026357325</v>
+        <v>205.0481221176458</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -25159,16 +25159,16 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>122.8486606547175</v>
+        <v>141.0252816852793</v>
       </c>
       <c r="S35" t="n">
-        <v>199.2180092847378</v>
+        <v>205.8118405263978</v>
       </c>
       <c r="T35" t="n">
-        <v>221.2128646395082</v>
+        <v>222.4795457699687</v>
       </c>
       <c r="U35" t="n">
-        <v>251.311240847535</v>
+        <v>251.3343897888113</v>
       </c>
       <c r="V35" t="n">
         <v>327.7522584701349</v>
@@ -25205,13 +25205,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G36" t="n">
-        <v>137.1133662198144</v>
+        <v>137.2681884137393</v>
       </c>
       <c r="H36" t="n">
-        <v>110.0126706515908</v>
+        <v>111.5079271034444</v>
       </c>
       <c r="I36" t="n">
-        <v>81.47257624764148</v>
+        <v>86.80307722268741</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -25238,16 +25238,16 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>85.8682869828318</v>
+        <v>95.48084390037957</v>
       </c>
       <c r="S36" t="n">
-        <v>167.4082182736491</v>
+        <v>170.2839726213331</v>
       </c>
       <c r="T36" t="n">
-        <v>199.2370588835009</v>
+        <v>199.8611009721718</v>
       </c>
       <c r="U36" t="n">
-        <v>225.9262405715409</v>
+        <v>225.9364262421938</v>
       </c>
       <c r="V36" t="n">
         <v>232.8005871494253</v>
@@ -25284,19 +25284,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G37" t="n">
-        <v>167.7980285387866</v>
+        <v>167.9278262653587</v>
       </c>
       <c r="H37" t="n">
-        <v>160.5116643107183</v>
+        <v>161.6656840978772</v>
       </c>
       <c r="I37" t="n">
-        <v>149.6479175502091</v>
+        <v>153.551289182031</v>
       </c>
       <c r="J37" t="n">
-        <v>79.71755716585311</v>
+        <v>88.89425643449839</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>14.93225064571201</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -25314,19 +25314,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>70.00504325169439</v>
+        <v>80.87383288310646</v>
       </c>
       <c r="R37" t="n">
-        <v>168.6176208853662</v>
+        <v>174.4537986637794</v>
       </c>
       <c r="S37" t="n">
-        <v>220.6539914795952</v>
+        <v>222.9160118599466</v>
       </c>
       <c r="T37" t="n">
-        <v>227.1211631987733</v>
+        <v>227.6757534850358</v>
       </c>
       <c r="U37" t="n">
-        <v>286.308504766327</v>
+        <v>286.3155846423218</v>
       </c>
       <c r="V37" t="n">
         <v>252.137643323828</v>
@@ -25363,13 +25363,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G38" t="n">
-        <v>414.8725867613662</v>
+        <v>415.1619485273195</v>
       </c>
       <c r="H38" t="n">
-        <v>335.069520708732</v>
+        <v>338.0329468943008</v>
       </c>
       <c r="I38" t="n">
-        <v>193.8925026357325</v>
+        <v>205.0481221176458</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -25396,16 +25396,16 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>122.8486606547175</v>
+        <v>141.0252816852793</v>
       </c>
       <c r="S38" t="n">
-        <v>199.2180092847378</v>
+        <v>205.8118405263978</v>
       </c>
       <c r="T38" t="n">
-        <v>221.2128646395082</v>
+        <v>222.4795457699687</v>
       </c>
       <c r="U38" t="n">
-        <v>251.311240847535</v>
+        <v>251.3343897888113</v>
       </c>
       <c r="V38" t="n">
         <v>327.7522584701349</v>
@@ -25442,13 +25442,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
-        <v>137.1133662198144</v>
+        <v>137.2681884137393</v>
       </c>
       <c r="H39" t="n">
-        <v>110.0126706515908</v>
+        <v>111.5079271034444</v>
       </c>
       <c r="I39" t="n">
-        <v>81.47257624764148</v>
+        <v>86.80307722268741</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -25475,16 +25475,16 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>85.8682869828318</v>
+        <v>95.48084390037957</v>
       </c>
       <c r="S39" t="n">
-        <v>167.4082182736491</v>
+        <v>170.2839726213331</v>
       </c>
       <c r="T39" t="n">
-        <v>199.2370588835009</v>
+        <v>199.8611009721718</v>
       </c>
       <c r="U39" t="n">
-        <v>225.9262405715409</v>
+        <v>225.9364262421938</v>
       </c>
       <c r="V39" t="n">
         <v>232.8005871494253</v>
@@ -25521,19 +25521,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G40" t="n">
-        <v>167.7980285387866</v>
+        <v>167.9278262653587</v>
       </c>
       <c r="H40" t="n">
-        <v>160.5116643107183</v>
+        <v>161.6656840978772</v>
       </c>
       <c r="I40" t="n">
-        <v>149.6479175502091</v>
+        <v>153.551289182031</v>
       </c>
       <c r="J40" t="n">
-        <v>79.71755716585311</v>
+        <v>88.89425643449839</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>14.93225064571201</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -25551,19 +25551,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>70.00504325169439</v>
+        <v>80.87383288310646</v>
       </c>
       <c r="R40" t="n">
-        <v>168.6176208853662</v>
+        <v>174.4537986637794</v>
       </c>
       <c r="S40" t="n">
-        <v>220.6539914795952</v>
+        <v>222.9160118599466</v>
       </c>
       <c r="T40" t="n">
-        <v>227.1211631987733</v>
+        <v>227.6757534850358</v>
       </c>
       <c r="U40" t="n">
-        <v>286.308504766327</v>
+        <v>286.3155846423218</v>
       </c>
       <c r="V40" t="n">
         <v>252.137643323828</v>
@@ -25600,13 +25600,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G41" t="n">
-        <v>414.8725867613662</v>
+        <v>415.1619485273195</v>
       </c>
       <c r="H41" t="n">
-        <v>335.069520708732</v>
+        <v>338.0329468943008</v>
       </c>
       <c r="I41" t="n">
-        <v>193.8925026357325</v>
+        <v>205.0481221176458</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -25633,16 +25633,16 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>122.8486606547175</v>
+        <v>141.0252816852793</v>
       </c>
       <c r="S41" t="n">
-        <v>199.2180092847378</v>
+        <v>205.8118405263978</v>
       </c>
       <c r="T41" t="n">
-        <v>221.2128646395082</v>
+        <v>222.4795457699687</v>
       </c>
       <c r="U41" t="n">
-        <v>251.311240847535</v>
+        <v>251.3343897888113</v>
       </c>
       <c r="V41" t="n">
         <v>327.7522584701349</v>
@@ -25679,13 +25679,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G42" t="n">
-        <v>137.1133662198144</v>
+        <v>137.2681884137393</v>
       </c>
       <c r="H42" t="n">
-        <v>110.0126706515908</v>
+        <v>111.5079271034444</v>
       </c>
       <c r="I42" t="n">
-        <v>81.47257624764148</v>
+        <v>86.80307722268741</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -25712,16 +25712,16 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>85.8682869828318</v>
+        <v>95.48084390037957</v>
       </c>
       <c r="S42" t="n">
-        <v>167.4082182736491</v>
+        <v>170.2839726213331</v>
       </c>
       <c r="T42" t="n">
-        <v>199.2370588835009</v>
+        <v>199.8611009721718</v>
       </c>
       <c r="U42" t="n">
-        <v>225.9262405715409</v>
+        <v>225.9364262421938</v>
       </c>
       <c r="V42" t="n">
         <v>232.8005871494253</v>
@@ -25758,19 +25758,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G43" t="n">
-        <v>167.7980285387866</v>
+        <v>167.9278262653587</v>
       </c>
       <c r="H43" t="n">
-        <v>160.5116643107183</v>
+        <v>161.6656840978772</v>
       </c>
       <c r="I43" t="n">
-        <v>149.6479175502091</v>
+        <v>153.551289182031</v>
       </c>
       <c r="J43" t="n">
-        <v>79.71755716585311</v>
+        <v>88.89425643449839</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>14.93225064571201</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -25788,19 +25788,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>70.00504325169439</v>
+        <v>80.87383288310646</v>
       </c>
       <c r="R43" t="n">
-        <v>168.6176208853662</v>
+        <v>174.4537986637794</v>
       </c>
       <c r="S43" t="n">
-        <v>220.6539914795952</v>
+        <v>222.9160118599466</v>
       </c>
       <c r="T43" t="n">
-        <v>227.1211631987733</v>
+        <v>227.6757534850358</v>
       </c>
       <c r="U43" t="n">
-        <v>286.308504766327</v>
+        <v>286.3155846423218</v>
       </c>
       <c r="V43" t="n">
         <v>252.137643323828</v>
@@ -25837,13 +25837,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G44" t="n">
-        <v>414.8725867613662</v>
+        <v>415.1619485273195</v>
       </c>
       <c r="H44" t="n">
-        <v>335.069520708732</v>
+        <v>338.0329468943008</v>
       </c>
       <c r="I44" t="n">
-        <v>193.8925026357325</v>
+        <v>205.0481221176458</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -25870,16 +25870,16 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>122.8486606547175</v>
+        <v>141.0252816852793</v>
       </c>
       <c r="S44" t="n">
-        <v>199.2180092847378</v>
+        <v>205.8118405263978</v>
       </c>
       <c r="T44" t="n">
-        <v>221.2128646395082</v>
+        <v>222.4795457699687</v>
       </c>
       <c r="U44" t="n">
-        <v>251.311240847535</v>
+        <v>251.3343897888113</v>
       </c>
       <c r="V44" t="n">
         <v>327.7522584701349</v>
@@ -25916,13 +25916,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G45" t="n">
-        <v>137.1133662198144</v>
+        <v>137.2681884137393</v>
       </c>
       <c r="H45" t="n">
-        <v>110.0126706515908</v>
+        <v>111.5079271034444</v>
       </c>
       <c r="I45" t="n">
-        <v>81.47257624764148</v>
+        <v>86.80307722268741</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -25949,16 +25949,16 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>85.8682869828318</v>
+        <v>95.48084390037957</v>
       </c>
       <c r="S45" t="n">
-        <v>167.4082182736491</v>
+        <v>170.2839726213331</v>
       </c>
       <c r="T45" t="n">
-        <v>199.2370588835009</v>
+        <v>199.8611009721718</v>
       </c>
       <c r="U45" t="n">
-        <v>225.9262405715409</v>
+        <v>225.9364262421938</v>
       </c>
       <c r="V45" t="n">
         <v>232.8005871494253</v>
@@ -25995,19 +25995,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G46" t="n">
-        <v>167.7980285387866</v>
+        <v>167.9278262653587</v>
       </c>
       <c r="H46" t="n">
-        <v>160.5116643107183</v>
+        <v>161.6656840978772</v>
       </c>
       <c r="I46" t="n">
-        <v>149.6479175502091</v>
+        <v>153.551289182031</v>
       </c>
       <c r="J46" t="n">
-        <v>79.71755716585311</v>
+        <v>88.89425643449839</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>14.93225064571201</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -26025,19 +26025,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>70.00504325169439</v>
+        <v>80.87383288310646</v>
       </c>
       <c r="R46" t="n">
-        <v>168.6176208853662</v>
+        <v>174.4537986637794</v>
       </c>
       <c r="S46" t="n">
-        <v>220.6539914795952</v>
+        <v>222.9160118599466</v>
       </c>
       <c r="T46" t="n">
-        <v>227.1211631987733</v>
+        <v>227.6757534850358</v>
       </c>
       <c r="U46" t="n">
-        <v>286.308504766327</v>
+        <v>286.3155846423218</v>
       </c>
       <c r="V46" t="n">
         <v>252.137643323828</v>
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>357609.9277943254</v>
+        <v>357750.4938645039</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>357609.9277943254</v>
+        <v>357750.4938645039</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>357609.9277943254</v>
+        <v>357750.4938645039</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>357609.9277943254</v>
+        <v>357750.4938645039</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>357609.9277943254</v>
+        <v>357750.4938645039</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>357609.9277943254</v>
+        <v>357750.4938645039</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>357609.9277943254</v>
+        <v>357750.4938645039</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>357609.9277943254</v>
+        <v>357750.4938645039</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>357609.9277943254</v>
+        <v>357750.4938645039</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>357609.9277943254</v>
+        <v>357750.4938645039</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>357609.9277943254</v>
+        <v>357750.4938645039</v>
       </c>
     </row>
     <row r="16">
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>357609.9277943254</v>
+        <v>357750.4938645039</v>
       </c>
     </row>
   </sheetData>
@@ -26261,49 +26261,49 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>64504.44331886782</v>
+      </c>
+      <c r="C2" t="n">
         <v>64504.44331886783</v>
       </c>
-      <c r="C2" t="n">
-        <v>64504.44331886784</v>
-      </c>
       <c r="D2" t="n">
-        <v>64504.44331886782</v>
+        <v>64504.44331886783</v>
       </c>
       <c r="E2" t="n">
-        <v>67397.27772594285</v>
+        <v>65823.63520640056</v>
       </c>
       <c r="F2" t="n">
-        <v>67397.27772594285</v>
+        <v>65823.63520640058</v>
       </c>
       <c r="G2" t="n">
-        <v>67397.27772594285</v>
+        <v>65823.63520640059</v>
       </c>
       <c r="H2" t="n">
-        <v>67397.27772594285</v>
+        <v>65823.63520640056</v>
       </c>
       <c r="I2" t="n">
-        <v>67397.27772594287</v>
+        <v>65823.63520640056</v>
       </c>
       <c r="J2" t="n">
-        <v>67397.27772594285</v>
+        <v>65823.63520640056</v>
       </c>
       <c r="K2" t="n">
-        <v>67397.27772594284</v>
+        <v>65823.63520640056</v>
       </c>
       <c r="L2" t="n">
-        <v>67397.27772594284</v>
+        <v>65823.63520640056</v>
       </c>
       <c r="M2" t="n">
-        <v>67397.27772594285</v>
+        <v>65823.63520640058</v>
       </c>
       <c r="N2" t="n">
-        <v>67397.27772594287</v>
+        <v>65823.63520640058</v>
       </c>
       <c r="O2" t="n">
-        <v>67397.27772594284</v>
+        <v>65823.63520640058</v>
       </c>
       <c r="P2" t="n">
-        <v>67397.27772594284</v>
+        <v>65823.63520640058</v>
       </c>
     </row>
     <row r="3">
@@ -26322,7 +26322,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>85964.121</v>
+        <v>28136.18592552744</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>43002.96221257856</v>
+        <v>41731.10116290394</v>
       </c>
       <c r="C4" t="n">
-        <v>43002.96221257856</v>
+        <v>41731.10116290394</v>
       </c>
       <c r="D4" t="n">
-        <v>43002.96221257856</v>
+        <v>41731.10116290394</v>
       </c>
       <c r="E4" t="n">
-        <v>31856.41878560125</v>
+        <v>38431.6226196582</v>
       </c>
       <c r="F4" t="n">
-        <v>31856.41878560125</v>
+        <v>38431.6226196582</v>
       </c>
       <c r="G4" t="n">
-        <v>31856.41878560125</v>
+        <v>38431.6226196582</v>
       </c>
       <c r="H4" t="n">
-        <v>31856.41878560125</v>
+        <v>38431.6226196582</v>
       </c>
       <c r="I4" t="n">
-        <v>31856.41878560125</v>
+        <v>38431.6226196582</v>
       </c>
       <c r="J4" t="n">
-        <v>31856.41878560125</v>
+        <v>38431.6226196582</v>
       </c>
       <c r="K4" t="n">
-        <v>31856.41878560125</v>
+        <v>38431.6226196582</v>
       </c>
       <c r="L4" t="n">
-        <v>31856.41878560125</v>
+        <v>38431.6226196582</v>
       </c>
       <c r="M4" t="n">
-        <v>31856.41878560125</v>
+        <v>38431.6226196582</v>
       </c>
       <c r="N4" t="n">
-        <v>31856.41878560125</v>
+        <v>38431.6226196582</v>
       </c>
       <c r="O4" t="n">
-        <v>31856.41878560125</v>
+        <v>38431.6226196582</v>
       </c>
       <c r="P4" t="n">
-        <v>31856.41878560125</v>
+        <v>38431.6226196582</v>
       </c>
     </row>
     <row r="5">
@@ -26426,40 +26426,40 @@
         <v>33627.6</v>
       </c>
       <c r="E5" t="n">
-        <v>2332.6</v>
+        <v>763.463483676932</v>
       </c>
       <c r="F5" t="n">
-        <v>2332.6</v>
+        <v>763.463483676932</v>
       </c>
       <c r="G5" t="n">
-        <v>2332.6</v>
+        <v>763.463483676932</v>
       </c>
       <c r="H5" t="n">
-        <v>2332.6</v>
+        <v>763.463483676932</v>
       </c>
       <c r="I5" t="n">
-        <v>2332.6</v>
+        <v>763.463483676932</v>
       </c>
       <c r="J5" t="n">
-        <v>2332.6</v>
+        <v>763.4634836769322</v>
       </c>
       <c r="K5" t="n">
-        <v>2332.6</v>
+        <v>763.463483676932</v>
       </c>
       <c r="L5" t="n">
-        <v>2332.6</v>
+        <v>763.463483676932</v>
       </c>
       <c r="M5" t="n">
-        <v>2332.6</v>
+        <v>763.463483676932</v>
       </c>
       <c r="N5" t="n">
-        <v>2332.6</v>
+        <v>763.463483676932</v>
       </c>
       <c r="O5" t="n">
-        <v>2332.6</v>
+        <v>763.463483676932</v>
       </c>
       <c r="P5" t="n">
-        <v>2332.6</v>
+        <v>763.463483676932</v>
       </c>
     </row>
     <row r="6">
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-12126.11889371073</v>
+        <v>-10854.25784403612</v>
       </c>
       <c r="C6" t="n">
-        <v>-12126.11889371072</v>
+        <v>-10854.25784403611</v>
       </c>
       <c r="D6" t="n">
-        <v>-12126.11889371074</v>
+        <v>-10854.25784403611</v>
       </c>
       <c r="E6" t="n">
-        <v>-52755.8620596584</v>
+        <v>-1507.636822462016</v>
       </c>
       <c r="F6" t="n">
-        <v>33208.2589403416</v>
+        <v>26628.54910306544</v>
       </c>
       <c r="G6" t="n">
-        <v>33208.2589403416</v>
+        <v>26628.54910306546</v>
       </c>
       <c r="H6" t="n">
-        <v>33208.2589403416</v>
+        <v>26628.54910306543</v>
       </c>
       <c r="I6" t="n">
-        <v>33208.25894034161</v>
+        <v>26628.54910306543</v>
       </c>
       <c r="J6" t="n">
-        <v>33208.2589403416</v>
+        <v>26628.54910306543</v>
       </c>
       <c r="K6" t="n">
-        <v>33208.25894034158</v>
+        <v>26628.54910306543</v>
       </c>
       <c r="L6" t="n">
-        <v>33208.25894034158</v>
+        <v>26628.54910306543</v>
       </c>
       <c r="M6" t="n">
-        <v>33208.2589403416</v>
+        <v>26628.54910306544</v>
       </c>
       <c r="N6" t="n">
-        <v>33208.25894034161</v>
+        <v>26628.54910306544</v>
       </c>
       <c r="O6" t="n">
-        <v>33208.25894034158</v>
+        <v>26628.54910306544</v>
       </c>
       <c r="P6" t="n">
-        <v>33208.25894034158</v>
+        <v>26628.54910306544</v>
       </c>
     </row>
   </sheetData>
@@ -26684,40 +26684,40 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>107</v>
+        <v>35.02126071912532</v>
       </c>
       <c r="F3" t="n">
-        <v>107</v>
+        <v>35.02126071912532</v>
       </c>
       <c r="G3" t="n">
-        <v>107</v>
+        <v>35.02126071912532</v>
       </c>
       <c r="H3" t="n">
-        <v>107</v>
+        <v>35.02126071912532</v>
       </c>
       <c r="I3" t="n">
-        <v>107</v>
+        <v>35.02126071912532</v>
       </c>
       <c r="J3" t="n">
-        <v>107</v>
+        <v>35.02126071912533</v>
       </c>
       <c r="K3" t="n">
-        <v>107</v>
+        <v>35.02126071912532</v>
       </c>
       <c r="L3" t="n">
-        <v>107</v>
+        <v>35.02126071912532</v>
       </c>
       <c r="M3" t="n">
-        <v>107</v>
+        <v>35.02126071912532</v>
       </c>
       <c r="N3" t="n">
-        <v>107</v>
+        <v>35.02126071912532</v>
       </c>
       <c r="O3" t="n">
-        <v>107</v>
+        <v>35.02126071912532</v>
       </c>
       <c r="P3" t="n">
-        <v>107</v>
+        <v>35.02126071912532</v>
       </c>
     </row>
     <row r="4">
@@ -26901,7 +26901,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>107</v>
+        <v>35.02126071912532</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -31670,49 +31670,49 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4301507537688439</v>
+        <v>0.1407889878155791</v>
       </c>
       <c r="H11" t="n">
-        <v>4.405281407035174</v>
+        <v>1.4418552214663</v>
       </c>
       <c r="I11" t="n">
-        <v>16.58338693467337</v>
+        <v>5.427767452760118</v>
       </c>
       <c r="J11" t="n">
-        <v>36.50850753768844</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K11" t="n">
-        <v>54.71678894472362</v>
+        <v>17.90888720884598</v>
       </c>
       <c r="L11" t="n">
-        <v>67.88101507537689</v>
+        <v>22.21755819470701</v>
       </c>
       <c r="M11" t="n">
-        <v>75.53070854271357</v>
+        <v>24.72131435677232</v>
       </c>
       <c r="N11" t="n">
-        <v>76.75287437185931</v>
+        <v>25.12133106840334</v>
       </c>
       <c r="O11" t="n">
-        <v>72.47556281407036</v>
+        <v>23.72136057081217</v>
       </c>
       <c r="P11" t="n">
-        <v>61.85621608040201</v>
+        <v>20.24563243411506</v>
       </c>
       <c r="Q11" t="n">
-        <v>46.45144221105527</v>
+        <v>15.20362680796963</v>
       </c>
       <c r="R11" t="n">
-        <v>27.02045728643217</v>
+        <v>8.843836255870377</v>
       </c>
       <c r="S11" t="n">
-        <v>9.80206030150754</v>
+        <v>3.208229059847512</v>
       </c>
       <c r="T11" t="n">
-        <v>1.882984924623115</v>
+        <v>0.6163037941626978</v>
       </c>
       <c r="U11" t="n">
-        <v>0.03441206030150751</v>
+        <v>0.01126311902524632</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -31749,49 +31749,49 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2301509433962264</v>
+        <v>0.07532874947132617</v>
       </c>
       <c r="H12" t="n">
-        <v>2.222773584905661</v>
+        <v>0.7275171330520186</v>
       </c>
       <c r="I12" t="n">
-        <v>7.924056603773586</v>
+        <v>2.593555628727678</v>
       </c>
       <c r="J12" t="n">
-        <v>21.74421698113208</v>
+        <v>7.116914878779988</v>
       </c>
       <c r="K12" t="n">
-        <v>37.16433018867925</v>
+        <v>12.16394109335884</v>
       </c>
       <c r="L12" t="n">
-        <v>49.9720283018868</v>
+        <v>16.35591992358773</v>
       </c>
       <c r="M12" t="n">
-        <v>58.31499999999999</v>
+        <v>19.0865870919233</v>
       </c>
       <c r="N12" t="n">
-        <v>59.85842452830189</v>
+        <v>19.59175225833408</v>
       </c>
       <c r="O12" t="n">
-        <v>54.7587641509434</v>
+        <v>17.92262575689049</v>
       </c>
       <c r="P12" t="n">
-        <v>43.94873584905661</v>
+        <v>14.38448725650263</v>
       </c>
       <c r="Q12" t="n">
-        <v>29.37856603773585</v>
+        <v>9.615648792164373</v>
       </c>
       <c r="R12" t="n">
-        <v>14.28954716981133</v>
+        <v>4.676990252263568</v>
       </c>
       <c r="S12" t="n">
-        <v>4.274952830188677</v>
+        <v>1.399198482504676</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9276698113207544</v>
+        <v>0.3036277226497751</v>
       </c>
       <c r="U12" t="n">
-        <v>0.01514150943396227</v>
+        <v>0.004955838781008303</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -31828,49 +31828,49 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1929508196721311</v>
+        <v>0.06315309310006205</v>
       </c>
       <c r="H13" t="n">
-        <v>1.715508196721313</v>
+        <v>0.5614884095623702</v>
       </c>
       <c r="I13" t="n">
-        <v>5.802557377049181</v>
+        <v>1.899185745227321</v>
       </c>
       <c r="J13" t="n">
-        <v>13.64162295081967</v>
+        <v>4.464923682174387</v>
       </c>
       <c r="K13" t="n">
-        <v>22.41737704918032</v>
+        <v>7.337241180170844</v>
       </c>
       <c r="L13" t="n">
-        <v>28.68652459016394</v>
+        <v>9.389142586894682</v>
       </c>
       <c r="M13" t="n">
-        <v>30.24591803278688</v>
+        <v>9.899534402948817</v>
       </c>
       <c r="N13" t="n">
-        <v>29.52673770491805</v>
+        <v>9.664145601394047</v>
       </c>
       <c r="O13" t="n">
-        <v>27.27272131147542</v>
+        <v>8.926402650179684</v>
       </c>
       <c r="P13" t="n">
-        <v>23.33652459016392</v>
+        <v>7.638079550938411</v>
       </c>
       <c r="Q13" t="n">
-        <v>16.157</v>
+        <v>5.288210368587923</v>
       </c>
       <c r="R13" t="n">
-        <v>8.675770491803275</v>
+        <v>2.839592713390062</v>
       </c>
       <c r="S13" t="n">
-        <v>3.362606557377048</v>
+        <v>1.100586177025626</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8244262295081964</v>
+        <v>0.2698359432457196</v>
       </c>
       <c r="U13" t="n">
-        <v>0.01052459016393444</v>
+        <v>0.003444714169094298</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -31907,49 +31907,49 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4301507537688439</v>
+        <v>0.1407889878155791</v>
       </c>
       <c r="H14" t="n">
-        <v>4.405281407035174</v>
+        <v>1.4418552214663</v>
       </c>
       <c r="I14" t="n">
-        <v>16.58338693467337</v>
+        <v>5.427767452760118</v>
       </c>
       <c r="J14" t="n">
-        <v>36.50850753768844</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K14" t="n">
-        <v>54.71678894472362</v>
+        <v>17.90888720884598</v>
       </c>
       <c r="L14" t="n">
-        <v>67.88101507537689</v>
+        <v>22.21755819470701</v>
       </c>
       <c r="M14" t="n">
-        <v>75.53070854271357</v>
+        <v>24.72131435677232</v>
       </c>
       <c r="N14" t="n">
-        <v>76.75287437185931</v>
+        <v>25.12133106840334</v>
       </c>
       <c r="O14" t="n">
-        <v>72.47556281407036</v>
+        <v>23.72136057081217</v>
       </c>
       <c r="P14" t="n">
-        <v>61.85621608040201</v>
+        <v>20.24563243411506</v>
       </c>
       <c r="Q14" t="n">
-        <v>46.45144221105527</v>
+        <v>15.20362680796963</v>
       </c>
       <c r="R14" t="n">
-        <v>27.02045728643217</v>
+        <v>8.843836255870377</v>
       </c>
       <c r="S14" t="n">
-        <v>9.80206030150754</v>
+        <v>3.208229059847512</v>
       </c>
       <c r="T14" t="n">
-        <v>1.882984924623115</v>
+        <v>0.6163037941626978</v>
       </c>
       <c r="U14" t="n">
-        <v>0.03441206030150751</v>
+        <v>0.01126311902524632</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -31986,49 +31986,49 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2301509433962264</v>
+        <v>0.07532874947132617</v>
       </c>
       <c r="H15" t="n">
-        <v>2.222773584905661</v>
+        <v>0.7275171330520186</v>
       </c>
       <c r="I15" t="n">
-        <v>7.924056603773586</v>
+        <v>2.593555628727678</v>
       </c>
       <c r="J15" t="n">
-        <v>21.74421698113208</v>
+        <v>7.116914878779988</v>
       </c>
       <c r="K15" t="n">
-        <v>37.16433018867925</v>
+        <v>12.16394109335884</v>
       </c>
       <c r="L15" t="n">
-        <v>49.9720283018868</v>
+        <v>16.35591992358773</v>
       </c>
       <c r="M15" t="n">
-        <v>58.31499999999999</v>
+        <v>19.0865870919233</v>
       </c>
       <c r="N15" t="n">
-        <v>59.85842452830189</v>
+        <v>19.59175225833408</v>
       </c>
       <c r="O15" t="n">
-        <v>54.7587641509434</v>
+        <v>17.92262575689049</v>
       </c>
       <c r="P15" t="n">
-        <v>43.94873584905661</v>
+        <v>14.38448725650263</v>
       </c>
       <c r="Q15" t="n">
-        <v>29.37856603773585</v>
+        <v>9.615648792164373</v>
       </c>
       <c r="R15" t="n">
-        <v>14.28954716981133</v>
+        <v>4.676990252263568</v>
       </c>
       <c r="S15" t="n">
-        <v>4.274952830188677</v>
+        <v>1.399198482504676</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9276698113207544</v>
+        <v>0.3036277226497751</v>
       </c>
       <c r="U15" t="n">
-        <v>0.01514150943396227</v>
+        <v>0.004955838781008303</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -32065,49 +32065,49 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1929508196721311</v>
+        <v>0.06315309310006205</v>
       </c>
       <c r="H16" t="n">
-        <v>1.715508196721313</v>
+        <v>0.5614884095623702</v>
       </c>
       <c r="I16" t="n">
-        <v>5.802557377049181</v>
+        <v>1.899185745227321</v>
       </c>
       <c r="J16" t="n">
-        <v>13.64162295081967</v>
+        <v>4.464923682174387</v>
       </c>
       <c r="K16" t="n">
-        <v>22.41737704918032</v>
+        <v>7.337241180170844</v>
       </c>
       <c r="L16" t="n">
-        <v>28.68652459016394</v>
+        <v>9.389142586894682</v>
       </c>
       <c r="M16" t="n">
-        <v>30.24591803278688</v>
+        <v>9.899534402948817</v>
       </c>
       <c r="N16" t="n">
-        <v>29.52673770491805</v>
+        <v>9.664145601394047</v>
       </c>
       <c r="O16" t="n">
-        <v>27.27272131147542</v>
+        <v>8.926402650179684</v>
       </c>
       <c r="P16" t="n">
-        <v>23.33652459016392</v>
+        <v>7.638079550938411</v>
       </c>
       <c r="Q16" t="n">
-        <v>16.157</v>
+        <v>5.288210368587923</v>
       </c>
       <c r="R16" t="n">
-        <v>8.675770491803275</v>
+        <v>2.839592713390062</v>
       </c>
       <c r="S16" t="n">
-        <v>3.362606557377048</v>
+        <v>1.100586177025626</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8244262295081964</v>
+        <v>0.2698359432457196</v>
       </c>
       <c r="U16" t="n">
-        <v>0.01052459016393444</v>
+        <v>0.003444714169094298</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -32144,49 +32144,49 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4301507537688439</v>
+        <v>0.1407889878155791</v>
       </c>
       <c r="H17" t="n">
-        <v>4.405281407035174</v>
+        <v>1.4418552214663</v>
       </c>
       <c r="I17" t="n">
-        <v>16.58338693467337</v>
+        <v>5.427767452760118</v>
       </c>
       <c r="J17" t="n">
-        <v>36.50850753768844</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K17" t="n">
-        <v>54.71678894472362</v>
+        <v>17.90888720884598</v>
       </c>
       <c r="L17" t="n">
-        <v>67.88101507537689</v>
+        <v>22.21755819470701</v>
       </c>
       <c r="M17" t="n">
-        <v>75.53070854271357</v>
+        <v>24.72131435677232</v>
       </c>
       <c r="N17" t="n">
-        <v>76.75287437185931</v>
+        <v>25.12133106840334</v>
       </c>
       <c r="O17" t="n">
-        <v>72.47556281407036</v>
+        <v>23.72136057081217</v>
       </c>
       <c r="P17" t="n">
-        <v>61.85621608040201</v>
+        <v>20.24563243411506</v>
       </c>
       <c r="Q17" t="n">
-        <v>46.45144221105527</v>
+        <v>15.20362680796963</v>
       </c>
       <c r="R17" t="n">
-        <v>27.02045728643217</v>
+        <v>8.843836255870377</v>
       </c>
       <c r="S17" t="n">
-        <v>9.80206030150754</v>
+        <v>3.208229059847512</v>
       </c>
       <c r="T17" t="n">
-        <v>1.882984924623115</v>
+        <v>0.6163037941626978</v>
       </c>
       <c r="U17" t="n">
-        <v>0.03441206030150751</v>
+        <v>0.01126311902524632</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -32223,49 +32223,49 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2301509433962264</v>
+        <v>0.07532874947132617</v>
       </c>
       <c r="H18" t="n">
-        <v>2.222773584905661</v>
+        <v>0.7275171330520186</v>
       </c>
       <c r="I18" t="n">
-        <v>7.924056603773586</v>
+        <v>2.593555628727678</v>
       </c>
       <c r="J18" t="n">
-        <v>21.74421698113208</v>
+        <v>7.116914878779988</v>
       </c>
       <c r="K18" t="n">
-        <v>37.16433018867925</v>
+        <v>12.16394109335884</v>
       </c>
       <c r="L18" t="n">
-        <v>49.9720283018868</v>
+        <v>16.35591992358773</v>
       </c>
       <c r="M18" t="n">
-        <v>58.31499999999999</v>
+        <v>19.0865870919233</v>
       </c>
       <c r="N18" t="n">
-        <v>59.85842452830189</v>
+        <v>19.59175225833408</v>
       </c>
       <c r="O18" t="n">
-        <v>54.7587641509434</v>
+        <v>17.92262575689049</v>
       </c>
       <c r="P18" t="n">
-        <v>43.94873584905661</v>
+        <v>14.38448725650263</v>
       </c>
       <c r="Q18" t="n">
-        <v>29.37856603773585</v>
+        <v>9.615648792164373</v>
       </c>
       <c r="R18" t="n">
-        <v>14.28954716981133</v>
+        <v>4.676990252263568</v>
       </c>
       <c r="S18" t="n">
-        <v>4.274952830188677</v>
+        <v>1.399198482504676</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9276698113207544</v>
+        <v>0.3036277226497751</v>
       </c>
       <c r="U18" t="n">
-        <v>0.01514150943396227</v>
+        <v>0.004955838781008303</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -32302,49 +32302,49 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1929508196721311</v>
+        <v>0.06315309310006205</v>
       </c>
       <c r="H19" t="n">
-        <v>1.715508196721313</v>
+        <v>0.5614884095623702</v>
       </c>
       <c r="I19" t="n">
-        <v>5.802557377049181</v>
+        <v>1.899185745227321</v>
       </c>
       <c r="J19" t="n">
-        <v>13.64162295081967</v>
+        <v>4.464923682174387</v>
       </c>
       <c r="K19" t="n">
-        <v>22.41737704918032</v>
+        <v>7.337241180170844</v>
       </c>
       <c r="L19" t="n">
-        <v>28.68652459016394</v>
+        <v>9.389142586894682</v>
       </c>
       <c r="M19" t="n">
-        <v>30.24591803278688</v>
+        <v>9.899534402948817</v>
       </c>
       <c r="N19" t="n">
-        <v>29.52673770491805</v>
+        <v>9.664145601394047</v>
       </c>
       <c r="O19" t="n">
-        <v>27.27272131147542</v>
+        <v>8.926402650179684</v>
       </c>
       <c r="P19" t="n">
-        <v>23.33652459016392</v>
+        <v>7.638079550938411</v>
       </c>
       <c r="Q19" t="n">
-        <v>16.157</v>
+        <v>5.288210368587923</v>
       </c>
       <c r="R19" t="n">
-        <v>8.675770491803275</v>
+        <v>2.839592713390062</v>
       </c>
       <c r="S19" t="n">
-        <v>3.362606557377048</v>
+        <v>1.100586177025626</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8244262295081964</v>
+        <v>0.2698359432457196</v>
       </c>
       <c r="U19" t="n">
-        <v>0.01052459016393444</v>
+        <v>0.003444714169094298</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -32381,49 +32381,49 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4301507537688439</v>
+        <v>0.1407889878155791</v>
       </c>
       <c r="H20" t="n">
-        <v>4.405281407035174</v>
+        <v>1.4418552214663</v>
       </c>
       <c r="I20" t="n">
-        <v>16.58338693467337</v>
+        <v>5.427767452760118</v>
       </c>
       <c r="J20" t="n">
-        <v>36.50850753768844</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K20" t="n">
-        <v>54.71678894472362</v>
+        <v>17.90888720884598</v>
       </c>
       <c r="L20" t="n">
-        <v>67.88101507537689</v>
+        <v>22.21755819470701</v>
       </c>
       <c r="M20" t="n">
-        <v>75.53070854271357</v>
+        <v>24.72131435677232</v>
       </c>
       <c r="N20" t="n">
-        <v>76.75287437185931</v>
+        <v>25.12133106840334</v>
       </c>
       <c r="O20" t="n">
-        <v>72.47556281407036</v>
+        <v>23.72136057081217</v>
       </c>
       <c r="P20" t="n">
-        <v>61.85621608040201</v>
+        <v>20.24563243411506</v>
       </c>
       <c r="Q20" t="n">
-        <v>46.45144221105527</v>
+        <v>15.20362680796963</v>
       </c>
       <c r="R20" t="n">
-        <v>27.02045728643217</v>
+        <v>8.843836255870377</v>
       </c>
       <c r="S20" t="n">
-        <v>9.80206030150754</v>
+        <v>3.208229059847512</v>
       </c>
       <c r="T20" t="n">
-        <v>1.882984924623115</v>
+        <v>0.6163037941626978</v>
       </c>
       <c r="U20" t="n">
-        <v>0.03441206030150751</v>
+        <v>0.01126311902524632</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -32460,49 +32460,49 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2301509433962264</v>
+        <v>0.07532874947132617</v>
       </c>
       <c r="H21" t="n">
-        <v>2.222773584905661</v>
+        <v>0.7275171330520186</v>
       </c>
       <c r="I21" t="n">
-        <v>7.924056603773586</v>
+        <v>2.593555628727678</v>
       </c>
       <c r="J21" t="n">
-        <v>21.74421698113208</v>
+        <v>7.116914878779988</v>
       </c>
       <c r="K21" t="n">
-        <v>37.16433018867925</v>
+        <v>12.16394109335884</v>
       </c>
       <c r="L21" t="n">
-        <v>49.9720283018868</v>
+        <v>16.35591992358773</v>
       </c>
       <c r="M21" t="n">
-        <v>58.31499999999999</v>
+        <v>19.0865870919233</v>
       </c>
       <c r="N21" t="n">
-        <v>59.85842452830189</v>
+        <v>19.59175225833408</v>
       </c>
       <c r="O21" t="n">
-        <v>54.7587641509434</v>
+        <v>17.92262575689049</v>
       </c>
       <c r="P21" t="n">
-        <v>43.94873584905661</v>
+        <v>14.38448725650263</v>
       </c>
       <c r="Q21" t="n">
-        <v>29.37856603773585</v>
+        <v>9.615648792164373</v>
       </c>
       <c r="R21" t="n">
-        <v>14.28954716981133</v>
+        <v>4.676990252263568</v>
       </c>
       <c r="S21" t="n">
-        <v>4.274952830188677</v>
+        <v>1.399198482504676</v>
       </c>
       <c r="T21" t="n">
-        <v>0.9276698113207544</v>
+        <v>0.3036277226497751</v>
       </c>
       <c r="U21" t="n">
-        <v>0.01514150943396227</v>
+        <v>0.004955838781008303</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -32539,49 +32539,49 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1929508196721311</v>
+        <v>0.06315309310006205</v>
       </c>
       <c r="H22" t="n">
-        <v>1.715508196721313</v>
+        <v>0.5614884095623702</v>
       </c>
       <c r="I22" t="n">
-        <v>5.802557377049181</v>
+        <v>1.899185745227321</v>
       </c>
       <c r="J22" t="n">
-        <v>13.64162295081967</v>
+        <v>4.464923682174387</v>
       </c>
       <c r="K22" t="n">
-        <v>22.41737704918032</v>
+        <v>7.337241180170844</v>
       </c>
       <c r="L22" t="n">
-        <v>28.68652459016394</v>
+        <v>9.389142586894682</v>
       </c>
       <c r="M22" t="n">
-        <v>30.24591803278688</v>
+        <v>9.899534402948817</v>
       </c>
       <c r="N22" t="n">
-        <v>29.52673770491805</v>
+        <v>9.664145601394047</v>
       </c>
       <c r="O22" t="n">
-        <v>27.27272131147542</v>
+        <v>8.926402650179684</v>
       </c>
       <c r="P22" t="n">
-        <v>23.33652459016392</v>
+        <v>7.638079550938411</v>
       </c>
       <c r="Q22" t="n">
-        <v>16.157</v>
+        <v>5.288210368587923</v>
       </c>
       <c r="R22" t="n">
-        <v>8.675770491803275</v>
+        <v>2.839592713390062</v>
       </c>
       <c r="S22" t="n">
-        <v>3.362606557377048</v>
+        <v>1.100586177025626</v>
       </c>
       <c r="T22" t="n">
-        <v>0.8244262295081964</v>
+        <v>0.2698359432457196</v>
       </c>
       <c r="U22" t="n">
-        <v>0.01052459016393444</v>
+        <v>0.003444714169094298</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -32618,49 +32618,49 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4301507537688439</v>
+        <v>0.1407889878155791</v>
       </c>
       <c r="H23" t="n">
-        <v>4.405281407035174</v>
+        <v>1.4418552214663</v>
       </c>
       <c r="I23" t="n">
-        <v>16.58338693467337</v>
+        <v>5.427767452760118</v>
       </c>
       <c r="J23" t="n">
-        <v>36.50850753768844</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K23" t="n">
-        <v>54.71678894472362</v>
+        <v>17.90888720884598</v>
       </c>
       <c r="L23" t="n">
-        <v>67.88101507537689</v>
+        <v>22.21755819470701</v>
       </c>
       <c r="M23" t="n">
-        <v>75.53070854271357</v>
+        <v>24.72131435677232</v>
       </c>
       <c r="N23" t="n">
-        <v>76.75287437185931</v>
+        <v>25.12133106840334</v>
       </c>
       <c r="O23" t="n">
-        <v>72.47556281407036</v>
+        <v>23.72136057081217</v>
       </c>
       <c r="P23" t="n">
-        <v>61.85621608040201</v>
+        <v>20.24563243411506</v>
       </c>
       <c r="Q23" t="n">
-        <v>46.45144221105527</v>
+        <v>15.20362680796963</v>
       </c>
       <c r="R23" t="n">
-        <v>27.02045728643217</v>
+        <v>8.843836255870377</v>
       </c>
       <c r="S23" t="n">
-        <v>9.80206030150754</v>
+        <v>3.208229059847512</v>
       </c>
       <c r="T23" t="n">
-        <v>1.882984924623115</v>
+        <v>0.6163037941626978</v>
       </c>
       <c r="U23" t="n">
-        <v>0.03441206030150751</v>
+        <v>0.01126311902524632</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -32697,49 +32697,49 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2301509433962264</v>
+        <v>0.07532874947132617</v>
       </c>
       <c r="H24" t="n">
-        <v>2.222773584905661</v>
+        <v>0.7275171330520186</v>
       </c>
       <c r="I24" t="n">
-        <v>7.924056603773586</v>
+        <v>2.593555628727678</v>
       </c>
       <c r="J24" t="n">
-        <v>21.74421698113208</v>
+        <v>7.116914878779988</v>
       </c>
       <c r="K24" t="n">
-        <v>37.16433018867925</v>
+        <v>12.16394109335884</v>
       </c>
       <c r="L24" t="n">
-        <v>49.9720283018868</v>
+        <v>16.35591992358773</v>
       </c>
       <c r="M24" t="n">
-        <v>58.31499999999999</v>
+        <v>19.0865870919233</v>
       </c>
       <c r="N24" t="n">
-        <v>59.85842452830189</v>
+        <v>19.59175225833408</v>
       </c>
       <c r="O24" t="n">
-        <v>54.7587641509434</v>
+        <v>17.92262575689049</v>
       </c>
       <c r="P24" t="n">
-        <v>43.94873584905661</v>
+        <v>14.38448725650263</v>
       </c>
       <c r="Q24" t="n">
-        <v>29.37856603773585</v>
+        <v>9.615648792164373</v>
       </c>
       <c r="R24" t="n">
-        <v>14.28954716981133</v>
+        <v>4.676990252263568</v>
       </c>
       <c r="S24" t="n">
-        <v>4.274952830188677</v>
+        <v>1.399198482504676</v>
       </c>
       <c r="T24" t="n">
-        <v>0.9276698113207544</v>
+        <v>0.3036277226497751</v>
       </c>
       <c r="U24" t="n">
-        <v>0.01514150943396227</v>
+        <v>0.004955838781008303</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -32776,49 +32776,49 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1929508196721311</v>
+        <v>0.06315309310006205</v>
       </c>
       <c r="H25" t="n">
-        <v>1.715508196721313</v>
+        <v>0.5614884095623702</v>
       </c>
       <c r="I25" t="n">
-        <v>5.802557377049181</v>
+        <v>1.899185745227321</v>
       </c>
       <c r="J25" t="n">
-        <v>13.64162295081967</v>
+        <v>4.464923682174387</v>
       </c>
       <c r="K25" t="n">
-        <v>22.41737704918032</v>
+        <v>7.337241180170844</v>
       </c>
       <c r="L25" t="n">
-        <v>28.68652459016394</v>
+        <v>9.389142586894682</v>
       </c>
       <c r="M25" t="n">
-        <v>30.24591803278688</v>
+        <v>9.899534402948817</v>
       </c>
       <c r="N25" t="n">
-        <v>29.52673770491805</v>
+        <v>9.664145601394047</v>
       </c>
       <c r="O25" t="n">
-        <v>27.27272131147542</v>
+        <v>8.926402650179684</v>
       </c>
       <c r="P25" t="n">
-        <v>23.33652459016392</v>
+        <v>7.638079550938411</v>
       </c>
       <c r="Q25" t="n">
-        <v>16.157</v>
+        <v>5.288210368587923</v>
       </c>
       <c r="R25" t="n">
-        <v>8.675770491803275</v>
+        <v>2.839592713390062</v>
       </c>
       <c r="S25" t="n">
-        <v>3.362606557377048</v>
+        <v>1.100586177025626</v>
       </c>
       <c r="T25" t="n">
-        <v>0.8244262295081964</v>
+        <v>0.2698359432457196</v>
       </c>
       <c r="U25" t="n">
-        <v>0.01052459016393444</v>
+        <v>0.003444714169094298</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -32855,49 +32855,49 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4301507537688439</v>
+        <v>0.1407889878155791</v>
       </c>
       <c r="H26" t="n">
-        <v>4.405281407035174</v>
+        <v>1.4418552214663</v>
       </c>
       <c r="I26" t="n">
-        <v>16.58338693467337</v>
+        <v>5.427767452760119</v>
       </c>
       <c r="J26" t="n">
-        <v>36.50850753768844</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K26" t="n">
-        <v>54.71678894472362</v>
+        <v>17.90888720884599</v>
       </c>
       <c r="L26" t="n">
-        <v>67.88101507537689</v>
+        <v>22.21755819470702</v>
       </c>
       <c r="M26" t="n">
-        <v>75.53070854271357</v>
+        <v>24.72131435677232</v>
       </c>
       <c r="N26" t="n">
-        <v>76.75287437185931</v>
+        <v>25.12133106840334</v>
       </c>
       <c r="O26" t="n">
-        <v>72.47556281407036</v>
+        <v>23.72136057081217</v>
       </c>
       <c r="P26" t="n">
-        <v>61.85621608040201</v>
+        <v>20.24563243411506</v>
       </c>
       <c r="Q26" t="n">
-        <v>46.45144221105527</v>
+        <v>15.20362680796963</v>
       </c>
       <c r="R26" t="n">
-        <v>27.02045728643217</v>
+        <v>8.843836255870377</v>
       </c>
       <c r="S26" t="n">
-        <v>9.80206030150754</v>
+        <v>3.208229059847512</v>
       </c>
       <c r="T26" t="n">
-        <v>1.882984924623115</v>
+        <v>0.6163037941626978</v>
       </c>
       <c r="U26" t="n">
-        <v>0.03441206030150751</v>
+        <v>0.01126311902524632</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -32934,49 +32934,49 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2301509433962264</v>
+        <v>0.07532874947132617</v>
       </c>
       <c r="H27" t="n">
-        <v>2.222773584905661</v>
+        <v>0.7275171330520187</v>
       </c>
       <c r="I27" t="n">
-        <v>7.924056603773586</v>
+        <v>2.593555628727678</v>
       </c>
       <c r="J27" t="n">
-        <v>21.74421698113208</v>
+        <v>7.116914878779989</v>
       </c>
       <c r="K27" t="n">
-        <v>37.16433018867925</v>
+        <v>12.16394109335884</v>
       </c>
       <c r="L27" t="n">
-        <v>49.9720283018868</v>
+        <v>16.35591992358773</v>
       </c>
       <c r="M27" t="n">
-        <v>58.31499999999999</v>
+        <v>19.0865870919233</v>
       </c>
       <c r="N27" t="n">
-        <v>59.85842452830189</v>
+        <v>19.59175225833408</v>
       </c>
       <c r="O27" t="n">
-        <v>54.7587641509434</v>
+        <v>17.92262575689049</v>
       </c>
       <c r="P27" t="n">
-        <v>43.94873584905661</v>
+        <v>14.38448725650263</v>
       </c>
       <c r="Q27" t="n">
-        <v>29.37856603773585</v>
+        <v>9.615648792164375</v>
       </c>
       <c r="R27" t="n">
-        <v>14.28954716981133</v>
+        <v>4.676990252263569</v>
       </c>
       <c r="S27" t="n">
-        <v>4.274952830188677</v>
+        <v>1.399198482504676</v>
       </c>
       <c r="T27" t="n">
-        <v>0.9276698113207544</v>
+        <v>0.3036277226497752</v>
       </c>
       <c r="U27" t="n">
-        <v>0.01514150943396227</v>
+        <v>0.004955838781008304</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -33013,49 +33013,49 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1929508196721311</v>
+        <v>0.06315309310006205</v>
       </c>
       <c r="H28" t="n">
-        <v>1.715508196721313</v>
+        <v>0.5614884095623703</v>
       </c>
       <c r="I28" t="n">
-        <v>5.802557377049181</v>
+        <v>1.899185745227321</v>
       </c>
       <c r="J28" t="n">
-        <v>13.64162295081967</v>
+        <v>4.464923682174387</v>
       </c>
       <c r="K28" t="n">
-        <v>22.41737704918032</v>
+        <v>7.337241180170845</v>
       </c>
       <c r="L28" t="n">
-        <v>28.68652459016394</v>
+        <v>9.389142586894682</v>
       </c>
       <c r="M28" t="n">
-        <v>30.24591803278688</v>
+        <v>9.899534402948818</v>
       </c>
       <c r="N28" t="n">
-        <v>29.52673770491805</v>
+        <v>9.664145601394049</v>
       </c>
       <c r="O28" t="n">
-        <v>27.27272131147542</v>
+        <v>8.926402650179684</v>
       </c>
       <c r="P28" t="n">
-        <v>23.33652459016392</v>
+        <v>7.638079550938412</v>
       </c>
       <c r="Q28" t="n">
-        <v>16.157</v>
+        <v>5.288210368587925</v>
       </c>
       <c r="R28" t="n">
-        <v>8.675770491803275</v>
+        <v>2.839592713390063</v>
       </c>
       <c r="S28" t="n">
-        <v>3.362606557377048</v>
+        <v>1.100586177025627</v>
       </c>
       <c r="T28" t="n">
-        <v>0.8244262295081964</v>
+        <v>0.2698359432457196</v>
       </c>
       <c r="U28" t="n">
-        <v>0.01052459016393444</v>
+        <v>0.003444714169094298</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -33092,49 +33092,49 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.4301507537688439</v>
+        <v>0.1407889878155791</v>
       </c>
       <c r="H29" t="n">
-        <v>4.405281407035174</v>
+        <v>1.4418552214663</v>
       </c>
       <c r="I29" t="n">
-        <v>16.58338693467337</v>
+        <v>5.427767452760118</v>
       </c>
       <c r="J29" t="n">
-        <v>36.50850753768844</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K29" t="n">
-        <v>54.71678894472362</v>
+        <v>17.90888720884598</v>
       </c>
       <c r="L29" t="n">
-        <v>67.88101507537689</v>
+        <v>22.21755819470701</v>
       </c>
       <c r="M29" t="n">
-        <v>75.53070854271357</v>
+        <v>24.72131435677232</v>
       </c>
       <c r="N29" t="n">
-        <v>76.75287437185931</v>
+        <v>25.12133106840334</v>
       </c>
       <c r="O29" t="n">
-        <v>72.47556281407036</v>
+        <v>23.72136057081217</v>
       </c>
       <c r="P29" t="n">
-        <v>61.85621608040201</v>
+        <v>20.24563243411506</v>
       </c>
       <c r="Q29" t="n">
-        <v>46.45144221105527</v>
+        <v>15.20362680796963</v>
       </c>
       <c r="R29" t="n">
-        <v>27.02045728643217</v>
+        <v>8.843836255870377</v>
       </c>
       <c r="S29" t="n">
-        <v>9.80206030150754</v>
+        <v>3.208229059847512</v>
       </c>
       <c r="T29" t="n">
-        <v>1.882984924623115</v>
+        <v>0.6163037941626978</v>
       </c>
       <c r="U29" t="n">
-        <v>0.03441206030150751</v>
+        <v>0.01126311902524632</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -33171,49 +33171,49 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2301509433962264</v>
+        <v>0.07532874947132617</v>
       </c>
       <c r="H30" t="n">
-        <v>2.222773584905661</v>
+        <v>0.7275171330520186</v>
       </c>
       <c r="I30" t="n">
-        <v>7.924056603773586</v>
+        <v>2.593555628727678</v>
       </c>
       <c r="J30" t="n">
-        <v>21.74421698113208</v>
+        <v>7.116914878779988</v>
       </c>
       <c r="K30" t="n">
-        <v>37.16433018867925</v>
+        <v>12.16394109335884</v>
       </c>
       <c r="L30" t="n">
-        <v>49.9720283018868</v>
+        <v>16.35591992358773</v>
       </c>
       <c r="M30" t="n">
-        <v>58.31499999999999</v>
+        <v>19.0865870919233</v>
       </c>
       <c r="N30" t="n">
-        <v>59.85842452830189</v>
+        <v>19.59175225833408</v>
       </c>
       <c r="O30" t="n">
-        <v>54.7587641509434</v>
+        <v>17.92262575689049</v>
       </c>
       <c r="P30" t="n">
-        <v>43.94873584905661</v>
+        <v>14.38448725650263</v>
       </c>
       <c r="Q30" t="n">
-        <v>29.37856603773585</v>
+        <v>9.615648792164373</v>
       </c>
       <c r="R30" t="n">
-        <v>14.28954716981133</v>
+        <v>4.676990252263568</v>
       </c>
       <c r="S30" t="n">
-        <v>4.274952830188677</v>
+        <v>1.399198482504676</v>
       </c>
       <c r="T30" t="n">
-        <v>0.9276698113207544</v>
+        <v>0.3036277226497751</v>
       </c>
       <c r="U30" t="n">
-        <v>0.01514150943396227</v>
+        <v>0.004955838781008303</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -33250,49 +33250,49 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1929508196721311</v>
+        <v>0.06315309310006205</v>
       </c>
       <c r="H31" t="n">
-        <v>1.715508196721313</v>
+        <v>0.5614884095623702</v>
       </c>
       <c r="I31" t="n">
-        <v>5.802557377049181</v>
+        <v>1.899185745227321</v>
       </c>
       <c r="J31" t="n">
-        <v>13.64162295081967</v>
+        <v>4.464923682174387</v>
       </c>
       <c r="K31" t="n">
-        <v>22.41737704918032</v>
+        <v>7.337241180170844</v>
       </c>
       <c r="L31" t="n">
-        <v>28.68652459016394</v>
+        <v>9.389142586894682</v>
       </c>
       <c r="M31" t="n">
-        <v>30.24591803278688</v>
+        <v>9.899534402948817</v>
       </c>
       <c r="N31" t="n">
-        <v>29.52673770491805</v>
+        <v>9.664145601394047</v>
       </c>
       <c r="O31" t="n">
-        <v>27.27272131147542</v>
+        <v>8.926402650179684</v>
       </c>
       <c r="P31" t="n">
-        <v>23.33652459016392</v>
+        <v>7.638079550938411</v>
       </c>
       <c r="Q31" t="n">
-        <v>16.157</v>
+        <v>5.288210368587923</v>
       </c>
       <c r="R31" t="n">
-        <v>8.675770491803275</v>
+        <v>2.839592713390062</v>
       </c>
       <c r="S31" t="n">
-        <v>3.362606557377048</v>
+        <v>1.100586177025626</v>
       </c>
       <c r="T31" t="n">
-        <v>0.8244262295081964</v>
+        <v>0.2698359432457196</v>
       </c>
       <c r="U31" t="n">
-        <v>0.01052459016393444</v>
+        <v>0.003444714169094298</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -33329,49 +33329,49 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.4301507537688439</v>
+        <v>0.1407889878155791</v>
       </c>
       <c r="H32" t="n">
-        <v>4.405281407035174</v>
+        <v>1.4418552214663</v>
       </c>
       <c r="I32" t="n">
-        <v>16.58338693467337</v>
+        <v>5.427767452760118</v>
       </c>
       <c r="J32" t="n">
-        <v>36.50850753768844</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K32" t="n">
-        <v>54.71678894472362</v>
+        <v>17.90888720884598</v>
       </c>
       <c r="L32" t="n">
-        <v>67.88101507537689</v>
+        <v>22.21755819470701</v>
       </c>
       <c r="M32" t="n">
-        <v>75.53070854271357</v>
+        <v>24.72131435677232</v>
       </c>
       <c r="N32" t="n">
-        <v>76.75287437185931</v>
+        <v>25.12133106840334</v>
       </c>
       <c r="O32" t="n">
-        <v>72.47556281407036</v>
+        <v>23.72136057081217</v>
       </c>
       <c r="P32" t="n">
-        <v>61.85621608040201</v>
+        <v>20.24563243411506</v>
       </c>
       <c r="Q32" t="n">
-        <v>46.45144221105527</v>
+        <v>15.20362680796963</v>
       </c>
       <c r="R32" t="n">
-        <v>27.02045728643217</v>
+        <v>8.843836255870377</v>
       </c>
       <c r="S32" t="n">
-        <v>9.80206030150754</v>
+        <v>3.208229059847512</v>
       </c>
       <c r="T32" t="n">
-        <v>1.882984924623115</v>
+        <v>0.6163037941626978</v>
       </c>
       <c r="U32" t="n">
-        <v>0.03441206030150751</v>
+        <v>0.01126311902524632</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -33408,49 +33408,49 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2301509433962264</v>
+        <v>0.07532874947132617</v>
       </c>
       <c r="H33" t="n">
-        <v>2.222773584905661</v>
+        <v>0.7275171330520186</v>
       </c>
       <c r="I33" t="n">
-        <v>7.924056603773586</v>
+        <v>2.593555628727678</v>
       </c>
       <c r="J33" t="n">
-        <v>21.74421698113208</v>
+        <v>7.116914878779988</v>
       </c>
       <c r="K33" t="n">
-        <v>37.16433018867925</v>
+        <v>12.16394109335884</v>
       </c>
       <c r="L33" t="n">
-        <v>49.9720283018868</v>
+        <v>16.35591992358773</v>
       </c>
       <c r="M33" t="n">
-        <v>58.31499999999999</v>
+        <v>19.0865870919233</v>
       </c>
       <c r="N33" t="n">
-        <v>59.85842452830189</v>
+        <v>19.59175225833408</v>
       </c>
       <c r="O33" t="n">
-        <v>54.7587641509434</v>
+        <v>17.92262575689049</v>
       </c>
       <c r="P33" t="n">
-        <v>43.94873584905661</v>
+        <v>14.38448725650263</v>
       </c>
       <c r="Q33" t="n">
-        <v>29.37856603773585</v>
+        <v>9.615648792164373</v>
       </c>
       <c r="R33" t="n">
-        <v>14.28954716981133</v>
+        <v>4.676990252263568</v>
       </c>
       <c r="S33" t="n">
-        <v>4.274952830188677</v>
+        <v>1.399198482504676</v>
       </c>
       <c r="T33" t="n">
-        <v>0.9276698113207544</v>
+        <v>0.3036277226497751</v>
       </c>
       <c r="U33" t="n">
-        <v>0.01514150943396227</v>
+        <v>0.004955838781008303</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -33487,49 +33487,49 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1929508196721311</v>
+        <v>0.06315309310006205</v>
       </c>
       <c r="H34" t="n">
-        <v>1.715508196721313</v>
+        <v>0.5614884095623702</v>
       </c>
       <c r="I34" t="n">
-        <v>5.802557377049181</v>
+        <v>1.899185745227321</v>
       </c>
       <c r="J34" t="n">
-        <v>13.64162295081967</v>
+        <v>4.464923682174387</v>
       </c>
       <c r="K34" t="n">
-        <v>22.41737704918032</v>
+        <v>7.337241180170844</v>
       </c>
       <c r="L34" t="n">
-        <v>28.68652459016394</v>
+        <v>9.389142586894682</v>
       </c>
       <c r="M34" t="n">
-        <v>30.24591803278688</v>
+        <v>9.899534402948817</v>
       </c>
       <c r="N34" t="n">
-        <v>29.52673770491805</v>
+        <v>9.664145601394047</v>
       </c>
       <c r="O34" t="n">
-        <v>27.27272131147542</v>
+        <v>8.926402650179684</v>
       </c>
       <c r="P34" t="n">
-        <v>23.33652459016392</v>
+        <v>7.638079550938411</v>
       </c>
       <c r="Q34" t="n">
-        <v>16.157</v>
+        <v>5.288210368587923</v>
       </c>
       <c r="R34" t="n">
-        <v>8.675770491803275</v>
+        <v>2.839592713390062</v>
       </c>
       <c r="S34" t="n">
-        <v>3.362606557377048</v>
+        <v>1.100586177025626</v>
       </c>
       <c r="T34" t="n">
-        <v>0.8244262295081964</v>
+        <v>0.2698359432457196</v>
       </c>
       <c r="U34" t="n">
-        <v>0.01052459016393444</v>
+        <v>0.003444714169094298</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -33566,49 +33566,49 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.4301507537688439</v>
+        <v>0.1407889878155791</v>
       </c>
       <c r="H35" t="n">
-        <v>4.405281407035174</v>
+        <v>1.4418552214663</v>
       </c>
       <c r="I35" t="n">
-        <v>16.58338693467337</v>
+        <v>5.427767452760118</v>
       </c>
       <c r="J35" t="n">
-        <v>36.50850753768844</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K35" t="n">
-        <v>54.71678894472362</v>
+        <v>17.90888720884598</v>
       </c>
       <c r="L35" t="n">
-        <v>67.88101507537689</v>
+        <v>22.21755819470701</v>
       </c>
       <c r="M35" t="n">
-        <v>75.53070854271357</v>
+        <v>24.72131435677232</v>
       </c>
       <c r="N35" t="n">
-        <v>76.75287437185931</v>
+        <v>25.12133106840334</v>
       </c>
       <c r="O35" t="n">
-        <v>72.47556281407036</v>
+        <v>23.72136057081217</v>
       </c>
       <c r="P35" t="n">
-        <v>61.85621608040201</v>
+        <v>20.24563243411506</v>
       </c>
       <c r="Q35" t="n">
-        <v>46.45144221105527</v>
+        <v>15.20362680796963</v>
       </c>
       <c r="R35" t="n">
-        <v>27.02045728643217</v>
+        <v>8.843836255870377</v>
       </c>
       <c r="S35" t="n">
-        <v>9.80206030150754</v>
+        <v>3.208229059847512</v>
       </c>
       <c r="T35" t="n">
-        <v>1.882984924623115</v>
+        <v>0.6163037941626978</v>
       </c>
       <c r="U35" t="n">
-        <v>0.03441206030150751</v>
+        <v>0.01126311902524632</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -33645,49 +33645,49 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.2301509433962264</v>
+        <v>0.07532874947132617</v>
       </c>
       <c r="H36" t="n">
-        <v>2.222773584905661</v>
+        <v>0.7275171330520186</v>
       </c>
       <c r="I36" t="n">
-        <v>7.924056603773586</v>
+        <v>2.593555628727678</v>
       </c>
       <c r="J36" t="n">
-        <v>21.74421698113208</v>
+        <v>7.116914878779988</v>
       </c>
       <c r="K36" t="n">
-        <v>37.16433018867925</v>
+        <v>12.16394109335884</v>
       </c>
       <c r="L36" t="n">
-        <v>49.9720283018868</v>
+        <v>16.35591992358773</v>
       </c>
       <c r="M36" t="n">
-        <v>58.31499999999999</v>
+        <v>19.0865870919233</v>
       </c>
       <c r="N36" t="n">
-        <v>59.85842452830189</v>
+        <v>19.59175225833408</v>
       </c>
       <c r="O36" t="n">
-        <v>54.7587641509434</v>
+        <v>17.92262575689049</v>
       </c>
       <c r="P36" t="n">
-        <v>43.94873584905661</v>
+        <v>14.38448725650263</v>
       </c>
       <c r="Q36" t="n">
-        <v>29.37856603773585</v>
+        <v>9.615648792164373</v>
       </c>
       <c r="R36" t="n">
-        <v>14.28954716981133</v>
+        <v>4.676990252263568</v>
       </c>
       <c r="S36" t="n">
-        <v>4.274952830188677</v>
+        <v>1.399198482504676</v>
       </c>
       <c r="T36" t="n">
-        <v>0.9276698113207544</v>
+        <v>0.3036277226497751</v>
       </c>
       <c r="U36" t="n">
-        <v>0.01514150943396227</v>
+        <v>0.004955838781008303</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -33724,49 +33724,49 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.1929508196721311</v>
+        <v>0.06315309310006205</v>
       </c>
       <c r="H37" t="n">
-        <v>1.715508196721313</v>
+        <v>0.5614884095623702</v>
       </c>
       <c r="I37" t="n">
-        <v>5.802557377049181</v>
+        <v>1.899185745227321</v>
       </c>
       <c r="J37" t="n">
-        <v>13.64162295081967</v>
+        <v>4.464923682174387</v>
       </c>
       <c r="K37" t="n">
-        <v>22.41737704918032</v>
+        <v>7.337241180170844</v>
       </c>
       <c r="L37" t="n">
-        <v>28.68652459016394</v>
+        <v>9.389142586894682</v>
       </c>
       <c r="M37" t="n">
-        <v>30.24591803278688</v>
+        <v>9.899534402948817</v>
       </c>
       <c r="N37" t="n">
-        <v>29.52673770491805</v>
+        <v>9.664145601394047</v>
       </c>
       <c r="O37" t="n">
-        <v>27.27272131147542</v>
+        <v>8.926402650179684</v>
       </c>
       <c r="P37" t="n">
-        <v>23.33652459016392</v>
+        <v>7.638079550938411</v>
       </c>
       <c r="Q37" t="n">
-        <v>16.157</v>
+        <v>5.288210368587923</v>
       </c>
       <c r="R37" t="n">
-        <v>8.675770491803275</v>
+        <v>2.839592713390062</v>
       </c>
       <c r="S37" t="n">
-        <v>3.362606557377048</v>
+        <v>1.100586177025626</v>
       </c>
       <c r="T37" t="n">
-        <v>0.8244262295081964</v>
+        <v>0.2698359432457196</v>
       </c>
       <c r="U37" t="n">
-        <v>0.01052459016393444</v>
+        <v>0.003444714169094298</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -33803,49 +33803,49 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0.4301507537688439</v>
+        <v>0.1407889878155791</v>
       </c>
       <c r="H38" t="n">
-        <v>4.405281407035174</v>
+        <v>1.4418552214663</v>
       </c>
       <c r="I38" t="n">
-        <v>16.58338693467337</v>
+        <v>5.427767452760118</v>
       </c>
       <c r="J38" t="n">
-        <v>36.50850753768844</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K38" t="n">
-        <v>54.71678894472362</v>
+        <v>17.90888720884598</v>
       </c>
       <c r="L38" t="n">
-        <v>67.88101507537689</v>
+        <v>22.21755819470701</v>
       </c>
       <c r="M38" t="n">
-        <v>75.53070854271357</v>
+        <v>24.72131435677232</v>
       </c>
       <c r="N38" t="n">
-        <v>76.75287437185931</v>
+        <v>25.12133106840334</v>
       </c>
       <c r="O38" t="n">
-        <v>72.47556281407036</v>
+        <v>23.72136057081217</v>
       </c>
       <c r="P38" t="n">
-        <v>61.85621608040201</v>
+        <v>20.24563243411506</v>
       </c>
       <c r="Q38" t="n">
-        <v>46.45144221105527</v>
+        <v>15.20362680796963</v>
       </c>
       <c r="R38" t="n">
-        <v>27.02045728643217</v>
+        <v>8.843836255870377</v>
       </c>
       <c r="S38" t="n">
-        <v>9.80206030150754</v>
+        <v>3.208229059847512</v>
       </c>
       <c r="T38" t="n">
-        <v>1.882984924623115</v>
+        <v>0.6163037941626978</v>
       </c>
       <c r="U38" t="n">
-        <v>0.03441206030150751</v>
+        <v>0.01126311902524632</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -33882,49 +33882,49 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.2301509433962264</v>
+        <v>0.07532874947132617</v>
       </c>
       <c r="H39" t="n">
-        <v>2.222773584905661</v>
+        <v>0.7275171330520186</v>
       </c>
       <c r="I39" t="n">
-        <v>7.924056603773586</v>
+        <v>2.593555628727678</v>
       </c>
       <c r="J39" t="n">
-        <v>21.74421698113208</v>
+        <v>7.116914878779988</v>
       </c>
       <c r="K39" t="n">
-        <v>37.16433018867925</v>
+        <v>12.16394109335884</v>
       </c>
       <c r="L39" t="n">
-        <v>49.9720283018868</v>
+        <v>16.35591992358773</v>
       </c>
       <c r="M39" t="n">
-        <v>58.31499999999999</v>
+        <v>19.0865870919233</v>
       </c>
       <c r="N39" t="n">
-        <v>59.85842452830189</v>
+        <v>19.59175225833408</v>
       </c>
       <c r="O39" t="n">
-        <v>54.7587641509434</v>
+        <v>17.92262575689049</v>
       </c>
       <c r="P39" t="n">
-        <v>43.94873584905661</v>
+        <v>14.38448725650263</v>
       </c>
       <c r="Q39" t="n">
-        <v>29.37856603773585</v>
+        <v>9.615648792164373</v>
       </c>
       <c r="R39" t="n">
-        <v>14.28954716981133</v>
+        <v>4.676990252263568</v>
       </c>
       <c r="S39" t="n">
-        <v>4.274952830188677</v>
+        <v>1.399198482504676</v>
       </c>
       <c r="T39" t="n">
-        <v>0.9276698113207544</v>
+        <v>0.3036277226497751</v>
       </c>
       <c r="U39" t="n">
-        <v>0.01514150943396227</v>
+        <v>0.004955838781008303</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -33961,49 +33961,49 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.1929508196721311</v>
+        <v>0.06315309310006205</v>
       </c>
       <c r="H40" t="n">
-        <v>1.715508196721313</v>
+        <v>0.5614884095623702</v>
       </c>
       <c r="I40" t="n">
-        <v>5.802557377049181</v>
+        <v>1.899185745227321</v>
       </c>
       <c r="J40" t="n">
-        <v>13.64162295081967</v>
+        <v>4.464923682174387</v>
       </c>
       <c r="K40" t="n">
-        <v>22.41737704918032</v>
+        <v>7.337241180170844</v>
       </c>
       <c r="L40" t="n">
-        <v>28.68652459016394</v>
+        <v>9.389142586894682</v>
       </c>
       <c r="M40" t="n">
-        <v>30.24591803278688</v>
+        <v>9.899534402948817</v>
       </c>
       <c r="N40" t="n">
-        <v>29.52673770491805</v>
+        <v>9.664145601394047</v>
       </c>
       <c r="O40" t="n">
-        <v>27.27272131147542</v>
+        <v>8.926402650179684</v>
       </c>
       <c r="P40" t="n">
-        <v>23.33652459016392</v>
+        <v>7.638079550938411</v>
       </c>
       <c r="Q40" t="n">
-        <v>16.157</v>
+        <v>5.288210368587923</v>
       </c>
       <c r="R40" t="n">
-        <v>8.675770491803275</v>
+        <v>2.839592713390062</v>
       </c>
       <c r="S40" t="n">
-        <v>3.362606557377048</v>
+        <v>1.100586177025626</v>
       </c>
       <c r="T40" t="n">
-        <v>0.8244262295081964</v>
+        <v>0.2698359432457196</v>
       </c>
       <c r="U40" t="n">
-        <v>0.01052459016393444</v>
+        <v>0.003444714169094298</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -34040,49 +34040,49 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0.4301507537688439</v>
+        <v>0.1407889878155791</v>
       </c>
       <c r="H41" t="n">
-        <v>4.405281407035174</v>
+        <v>1.4418552214663</v>
       </c>
       <c r="I41" t="n">
-        <v>16.58338693467337</v>
+        <v>5.427767452760118</v>
       </c>
       <c r="J41" t="n">
-        <v>36.50850753768844</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K41" t="n">
-        <v>54.71678894472362</v>
+        <v>17.90888720884598</v>
       </c>
       <c r="L41" t="n">
-        <v>67.88101507537689</v>
+        <v>22.21755819470701</v>
       </c>
       <c r="M41" t="n">
-        <v>75.53070854271357</v>
+        <v>24.72131435677232</v>
       </c>
       <c r="N41" t="n">
-        <v>76.75287437185931</v>
+        <v>25.12133106840334</v>
       </c>
       <c r="O41" t="n">
-        <v>72.47556281407036</v>
+        <v>23.72136057081217</v>
       </c>
       <c r="P41" t="n">
-        <v>61.85621608040201</v>
+        <v>20.24563243411506</v>
       </c>
       <c r="Q41" t="n">
-        <v>46.45144221105527</v>
+        <v>15.20362680796963</v>
       </c>
       <c r="R41" t="n">
-        <v>27.02045728643217</v>
+        <v>8.843836255870377</v>
       </c>
       <c r="S41" t="n">
-        <v>9.80206030150754</v>
+        <v>3.208229059847512</v>
       </c>
       <c r="T41" t="n">
-        <v>1.882984924623115</v>
+        <v>0.6163037941626978</v>
       </c>
       <c r="U41" t="n">
-        <v>0.03441206030150751</v>
+        <v>0.01126311902524632</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -34119,49 +34119,49 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.2301509433962264</v>
+        <v>0.07532874947132617</v>
       </c>
       <c r="H42" t="n">
-        <v>2.222773584905661</v>
+        <v>0.7275171330520186</v>
       </c>
       <c r="I42" t="n">
-        <v>7.924056603773586</v>
+        <v>2.593555628727678</v>
       </c>
       <c r="J42" t="n">
-        <v>21.74421698113208</v>
+        <v>7.116914878779988</v>
       </c>
       <c r="K42" t="n">
-        <v>37.16433018867925</v>
+        <v>12.16394109335884</v>
       </c>
       <c r="L42" t="n">
-        <v>49.9720283018868</v>
+        <v>16.35591992358773</v>
       </c>
       <c r="M42" t="n">
-        <v>58.31499999999999</v>
+        <v>19.0865870919233</v>
       </c>
       <c r="N42" t="n">
-        <v>59.85842452830189</v>
+        <v>19.59175225833408</v>
       </c>
       <c r="O42" t="n">
-        <v>54.7587641509434</v>
+        <v>17.92262575689049</v>
       </c>
       <c r="P42" t="n">
-        <v>43.94873584905661</v>
+        <v>14.38448725650263</v>
       </c>
       <c r="Q42" t="n">
-        <v>29.37856603773585</v>
+        <v>9.615648792164373</v>
       </c>
       <c r="R42" t="n">
-        <v>14.28954716981133</v>
+        <v>4.676990252263568</v>
       </c>
       <c r="S42" t="n">
-        <v>4.274952830188677</v>
+        <v>1.399198482504676</v>
       </c>
       <c r="T42" t="n">
-        <v>0.9276698113207544</v>
+        <v>0.3036277226497751</v>
       </c>
       <c r="U42" t="n">
-        <v>0.01514150943396227</v>
+        <v>0.004955838781008303</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -34198,49 +34198,49 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.1929508196721311</v>
+        <v>0.06315309310006205</v>
       </c>
       <c r="H43" t="n">
-        <v>1.715508196721313</v>
+        <v>0.5614884095623702</v>
       </c>
       <c r="I43" t="n">
-        <v>5.802557377049181</v>
+        <v>1.899185745227321</v>
       </c>
       <c r="J43" t="n">
-        <v>13.64162295081967</v>
+        <v>4.464923682174387</v>
       </c>
       <c r="K43" t="n">
-        <v>22.41737704918032</v>
+        <v>7.337241180170844</v>
       </c>
       <c r="L43" t="n">
-        <v>28.68652459016394</v>
+        <v>9.389142586894682</v>
       </c>
       <c r="M43" t="n">
-        <v>30.24591803278688</v>
+        <v>9.899534402948817</v>
       </c>
       <c r="N43" t="n">
-        <v>29.52673770491805</v>
+        <v>9.664145601394047</v>
       </c>
       <c r="O43" t="n">
-        <v>27.27272131147542</v>
+        <v>8.926402650179684</v>
       </c>
       <c r="P43" t="n">
-        <v>23.33652459016392</v>
+        <v>7.638079550938411</v>
       </c>
       <c r="Q43" t="n">
-        <v>16.157</v>
+        <v>5.288210368587923</v>
       </c>
       <c r="R43" t="n">
-        <v>8.675770491803275</v>
+        <v>2.839592713390062</v>
       </c>
       <c r="S43" t="n">
-        <v>3.362606557377048</v>
+        <v>1.100586177025626</v>
       </c>
       <c r="T43" t="n">
-        <v>0.8244262295081964</v>
+        <v>0.2698359432457196</v>
       </c>
       <c r="U43" t="n">
-        <v>0.01052459016393444</v>
+        <v>0.003444714169094298</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -34277,49 +34277,49 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0.4301507537688439</v>
+        <v>0.1407889878155791</v>
       </c>
       <c r="H44" t="n">
-        <v>4.405281407035174</v>
+        <v>1.4418552214663</v>
       </c>
       <c r="I44" t="n">
-        <v>16.58338693467337</v>
+        <v>5.427767452760118</v>
       </c>
       <c r="J44" t="n">
-        <v>36.50850753768844</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K44" t="n">
-        <v>54.71678894472362</v>
+        <v>17.90888720884598</v>
       </c>
       <c r="L44" t="n">
-        <v>67.88101507537689</v>
+        <v>22.21755819470701</v>
       </c>
       <c r="M44" t="n">
-        <v>75.53070854271357</v>
+        <v>24.72131435677232</v>
       </c>
       <c r="N44" t="n">
-        <v>76.75287437185931</v>
+        <v>25.12133106840334</v>
       </c>
       <c r="O44" t="n">
-        <v>72.47556281407036</v>
+        <v>23.72136057081217</v>
       </c>
       <c r="P44" t="n">
-        <v>61.85621608040201</v>
+        <v>20.24563243411506</v>
       </c>
       <c r="Q44" t="n">
-        <v>46.45144221105527</v>
+        <v>15.20362680796963</v>
       </c>
       <c r="R44" t="n">
-        <v>27.02045728643217</v>
+        <v>8.843836255870377</v>
       </c>
       <c r="S44" t="n">
-        <v>9.80206030150754</v>
+        <v>3.208229059847512</v>
       </c>
       <c r="T44" t="n">
-        <v>1.882984924623115</v>
+        <v>0.6163037941626978</v>
       </c>
       <c r="U44" t="n">
-        <v>0.03441206030150751</v>
+        <v>0.01126311902524632</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -34356,49 +34356,49 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.2301509433962264</v>
+        <v>0.07532874947132617</v>
       </c>
       <c r="H45" t="n">
-        <v>2.222773584905661</v>
+        <v>0.7275171330520186</v>
       </c>
       <c r="I45" t="n">
-        <v>7.924056603773586</v>
+        <v>2.593555628727678</v>
       </c>
       <c r="J45" t="n">
-        <v>21.74421698113208</v>
+        <v>7.116914878779988</v>
       </c>
       <c r="K45" t="n">
-        <v>37.16433018867925</v>
+        <v>12.16394109335884</v>
       </c>
       <c r="L45" t="n">
-        <v>49.9720283018868</v>
+        <v>16.35591992358773</v>
       </c>
       <c r="M45" t="n">
-        <v>58.31499999999999</v>
+        <v>19.0865870919233</v>
       </c>
       <c r="N45" t="n">
-        <v>59.85842452830189</v>
+        <v>19.59175225833408</v>
       </c>
       <c r="O45" t="n">
-        <v>54.7587641509434</v>
+        <v>17.92262575689049</v>
       </c>
       <c r="P45" t="n">
-        <v>43.94873584905661</v>
+        <v>14.38448725650263</v>
       </c>
       <c r="Q45" t="n">
-        <v>29.37856603773585</v>
+        <v>9.615648792164373</v>
       </c>
       <c r="R45" t="n">
-        <v>14.28954716981133</v>
+        <v>4.676990252263568</v>
       </c>
       <c r="S45" t="n">
-        <v>4.274952830188677</v>
+        <v>1.399198482504676</v>
       </c>
       <c r="T45" t="n">
-        <v>0.9276698113207544</v>
+        <v>0.3036277226497751</v>
       </c>
       <c r="U45" t="n">
-        <v>0.01514150943396227</v>
+        <v>0.004955838781008303</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -34435,49 +34435,49 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.1929508196721311</v>
+        <v>0.06315309310006205</v>
       </c>
       <c r="H46" t="n">
-        <v>1.715508196721313</v>
+        <v>0.5614884095623702</v>
       </c>
       <c r="I46" t="n">
-        <v>5.802557377049181</v>
+        <v>1.899185745227321</v>
       </c>
       <c r="J46" t="n">
-        <v>13.64162295081967</v>
+        <v>4.464923682174387</v>
       </c>
       <c r="K46" t="n">
-        <v>22.41737704918032</v>
+        <v>7.337241180170844</v>
       </c>
       <c r="L46" t="n">
-        <v>28.68652459016394</v>
+        <v>9.389142586894682</v>
       </c>
       <c r="M46" t="n">
-        <v>30.24591803278688</v>
+        <v>9.899534402948817</v>
       </c>
       <c r="N46" t="n">
-        <v>29.52673770491805</v>
+        <v>9.664145601394047</v>
       </c>
       <c r="O46" t="n">
-        <v>27.27272131147542</v>
+        <v>8.926402650179684</v>
       </c>
       <c r="P46" t="n">
-        <v>23.33652459016392</v>
+        <v>7.638079550938411</v>
       </c>
       <c r="Q46" t="n">
-        <v>16.157</v>
+        <v>5.288210368587923</v>
       </c>
       <c r="R46" t="n">
-        <v>8.675770491803275</v>
+        <v>2.839592713390062</v>
       </c>
       <c r="S46" t="n">
-        <v>3.362606557377048</v>
+        <v>1.100586177025626</v>
       </c>
       <c r="T46" t="n">
-        <v>0.8244262295081964</v>
+        <v>0.2698359432457196</v>
       </c>
       <c r="U46" t="n">
-        <v>0.01052459016393444</v>
+        <v>0.003444714169094298</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
